--- a/ARM Functions/Other Mechanics/Ultra Burst.xlsx
+++ b/ARM Functions/Other Mechanics/Ultra Burst.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\ROM\3ds\USUM ARM research\Other Mechanics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9540B541-DBF4-4A41-ACCD-76AF66C10B02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AE890EB-6C55-4EED-AC9A-4BC6872E85F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18120" xr2:uid="{FFF8744C-F0B4-428F-8CA7-718350CADE02}"/>
+    <workbookView xWindow="-16466" yWindow="0" windowWidth="16466" windowHeight="17914" xr2:uid="{FFF8744C-F0B4-428F-8CA7-718350CADE02}"/>
   </bookViews>
   <sheets>
     <sheet name="Table of Ultra Bursts" sheetId="9" r:id="rId1"/>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2982" uniqueCount="2297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2998" uniqueCount="2321">
   <si>
     <t>Address</t>
   </si>
@@ -6451,9 +6451,6 @@
     <t>90201FE5</t>
   </si>
   <si>
-    <t>00144BC8</t>
-  </si>
-  <si>
     <t>if current forme &lt; loaded forme from table, return 1</t>
   </si>
   <si>
@@ -6956,6 +6953,81 @@
   </si>
   <si>
     <t>TM115</t>
+  </si>
+  <si>
+    <t>Meganiumite</t>
+  </si>
+  <si>
+    <t>Machampinite</t>
+  </si>
+  <si>
+    <t>Lurantinite</t>
+  </si>
+  <si>
+    <t>Araquanite</t>
+  </si>
+  <si>
+    <t>Cherriminite</t>
+  </si>
+  <si>
+    <t>Ribombinite</t>
+  </si>
+  <si>
+    <t>Crabominite</t>
+  </si>
+  <si>
+    <t>Drampanite</t>
+  </si>
+  <si>
+    <t>Excadrite</t>
+  </si>
+  <si>
+    <t>Emboarite</t>
+  </si>
+  <si>
+    <t>Hawluchanite</t>
+  </si>
+  <si>
+    <t>Meowsticite</t>
+  </si>
+  <si>
+    <t>Starminite</t>
+  </si>
+  <si>
+    <t>Raichunite X</t>
+  </si>
+  <si>
+    <t>Raichunite Y</t>
+  </si>
+  <si>
+    <t>00148BC8</t>
+  </si>
+  <si>
+    <t>Squirtilium U</t>
+  </si>
+  <si>
+    <t>Dragalgite</t>
+  </si>
+  <si>
+    <t>Eelektrossite</t>
+  </si>
+  <si>
+    <t>Gumshoosinite</t>
+  </si>
+  <si>
+    <t>Malamarite</t>
+  </si>
+  <si>
+    <t>Pyroarite</t>
+  </si>
+  <si>
+    <t>Scolipite</t>
+  </si>
+  <si>
+    <t>Scraftinite</t>
+  </si>
+  <si>
+    <t>Staraptite</t>
   </si>
 </sst>
 </file>
@@ -7687,7 +7759,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61031E4B-3830-4323-AD27-09A246955145}">
-  <dimension ref="A1:J52"/>
+  <dimension ref="A1:J60"/>
   <sheetFormatPr defaultRowHeight="14.15"/>
   <cols>
     <col min="1" max="1" width="10.35546875" customWidth="1"/>
@@ -7744,7 +7816,7 @@
         <v>266</v>
       </c>
       <c r="E2" t="str">
-        <f t="shared" ref="E2:E10" si="0">_xlfn.CONCAT(A2," ",C2)</f>
+        <f t="shared" ref="E2:E13" si="0">_xlfn.CONCAT(A2," ",C2)</f>
         <v>Raticate 2</v>
       </c>
       <c r="F2">
@@ -7752,7 +7824,7 @@
         <v>20</v>
       </c>
       <c r="G2" t="str">
-        <f t="shared" ref="G2" si="1">IF(F2&lt;&gt;"",DEC2HEX(F2,4),"")</f>
+        <f t="shared" ref="G2:G13" si="1">IF(F2&lt;&gt;"",DEC2HEX(F2,4),"")</f>
         <v>0014</v>
       </c>
       <c r="H2" t="str" cm="1">
@@ -7760,7 +7832,7 @@
         <v>14009B0302FF</v>
       </c>
       <c r="I2" t="str">
-        <f t="shared" ref="I2" si="2">IF(OR(A2&lt;&gt;A1,C2&lt;&gt;C1),LEFT(H2,4)&amp;LEFT(RIGHT(H2,4),2),"")</f>
+        <f t="shared" ref="I2:I13" si="2">IF(OR(A2&lt;&gt;A1,C2&lt;&gt;C1),LEFT(H2,4)&amp;LEFT(RIGHT(H2,4),2),"")</f>
         <v>140002</v>
       </c>
       <c r="J2">
@@ -7770,41 +7842,41 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>143</v>
+        <v>307</v>
       </c>
       <c r="B3">
         <v>255</v>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>1594</v>
+        <v>2309</v>
       </c>
       <c r="E3" t="str">
         <f t="shared" si="0"/>
-        <v>Persian 3</v>
+        <v>Raichu 2</v>
       </c>
       <c r="F3">
         <f>IF(AND(A3&lt;&gt;"",ISNUMBER(C3),D3&lt;&gt;""),_xlfn.XLOOKUP(A3,'Table of IDs'!M:M,'Table of IDs'!L:L),"")</f>
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="G3" t="str">
-        <f t="shared" ref="G3:G52" si="3">IF(F3&lt;&gt;"",DEC2HEX(F3,4),"")</f>
-        <v>0035</v>
+        <f t="shared" si="1"/>
+        <v>001A</v>
       </c>
       <c r="H3" t="str" cm="1">
         <f t="array" ref="H3">IF(G3&lt;&gt;"",RIGHT(G3,2)&amp;LEFT(G3,2)&amp;_xlfn.XLOOKUP(D3,'Table of IDs'!$C:C,'Table of IDs'!D:D)&amp;DEC2HEX(C3,2)&amp;DEC2HEX(B3,2),"")</f>
-        <v>3500460103FF</v>
+        <v>1A006E0302FF</v>
       </c>
       <c r="I3" t="str">
-        <f t="shared" ref="I3:I52" si="4">IF(OR(A3&lt;&gt;A2,C3&lt;&gt;C2),LEFT(H3,4)&amp;LEFT(RIGHT(H3,4),2),"")</f>
-        <v>350003</v>
+        <f t="shared" si="2"/>
+        <v>1A0002</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>143</v>
+        <v>307</v>
       </c>
       <c r="B4">
         <v>255</v>
@@ -7813,100 +7885,100 @@
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>1595</v>
+        <v>2310</v>
       </c>
       <c r="E4" t="str">
         <f t="shared" si="0"/>
-        <v>Persian 3</v>
+        <v>Raichu 3</v>
       </c>
       <c r="F4">
         <f>IF(AND(A4&lt;&gt;"",ISNUMBER(C4),D4&lt;&gt;""),_xlfn.XLOOKUP(A4,'Table of IDs'!M:M,'Table of IDs'!L:L),"")</f>
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="G4" t="str">
-        <f t="shared" si="3"/>
-        <v>0035</v>
+        <f t="shared" si="1"/>
+        <v>001A</v>
       </c>
       <c r="H4" t="str" cm="1">
         <f t="array" ref="H4">IF(G4&lt;&gt;"",RIGHT(G4,2)&amp;LEFT(G4,2)&amp;_xlfn.XLOOKUP(D4,'Table of IDs'!$C:C,'Table of IDs'!D:D)&amp;DEC2HEX(C4,2)&amp;DEC2HEX(B4,2),"")</f>
-        <v>3500470103FF</v>
+        <v>1A007C0303FF</v>
       </c>
       <c r="I4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
+        <f t="shared" si="2"/>
+        <v>1A0003</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>143</v>
+        <v>307</v>
       </c>
       <c r="B5">
-        <v>255</v>
+        <v>0</v>
       </c>
       <c r="C5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D5" t="s">
-        <v>266</v>
+        <v>245</v>
       </c>
       <c r="E5" t="str">
         <f t="shared" si="0"/>
-        <v>Persian 3</v>
+        <v>Raichu 2</v>
       </c>
       <c r="F5">
         <f>IF(AND(A5&lt;&gt;"",ISNUMBER(C5),D5&lt;&gt;""),_xlfn.XLOOKUP(A5,'Table of IDs'!M:M,'Table of IDs'!L:L),"")</f>
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="G5" t="str">
-        <f t="shared" si="3"/>
-        <v>0035</v>
+        <f t="shared" si="1"/>
+        <v>001A</v>
       </c>
       <c r="H5" t="str" cm="1">
         <f t="array" ref="H5">IF(G5&lt;&gt;"",RIGHT(G5,2)&amp;LEFT(G5,2)&amp;_xlfn.XLOOKUP(D5,'Table of IDs'!$C:C,'Table of IDs'!D:D)&amp;DEC2HEX(C5,2)&amp;DEC2HEX(B5,2),"")</f>
-        <v>35009B0303FF</v>
+        <v>1A0023030200</v>
       </c>
       <c r="I5" t="str">
-        <f t="shared" si="4"/>
-        <v/>
+        <f t="shared" si="2"/>
+        <v>1A0002</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>150</v>
+        <v>307</v>
       </c>
       <c r="B6">
-        <v>255</v>
+        <v>1</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6" t="s">
-        <v>1910</v>
+        <v>245</v>
       </c>
       <c r="E6" t="str">
         <f t="shared" si="0"/>
-        <v>Slowbro 2</v>
+        <v>Raichu 3</v>
       </c>
       <c r="F6">
         <f>IF(AND(A6&lt;&gt;"",ISNUMBER(C6),D6&lt;&gt;""),_xlfn.XLOOKUP(A6,'Table of IDs'!M:M,'Table of IDs'!L:L),"")</f>
-        <v>80</v>
+        <v>26</v>
       </c>
       <c r="G6" t="str">
-        <f t="shared" si="3"/>
-        <v>0050</v>
+        <f t="shared" si="1"/>
+        <v>001A</v>
       </c>
       <c r="H6" t="str" cm="1">
         <f t="array" ref="H6">IF(G6&lt;&gt;"",RIGHT(G6,2)&amp;LEFT(G6,2)&amp;_xlfn.XLOOKUP(D6,'Table of IDs'!$C:C,'Table of IDs'!D:D)&amp;DEC2HEX(C6,2)&amp;DEC2HEX(B6,2),"")</f>
-        <v>5000F80202FF</v>
+        <v>1A0023030301</v>
       </c>
       <c r="I6" t="str">
-        <f t="shared" si="4"/>
-        <v>500002</v>
+        <f t="shared" si="2"/>
+        <v>1A0003</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>382</v>
+        <v>143</v>
       </c>
       <c r="B7">
         <v>255</v>
@@ -7915,66 +7987,66 @@
         <v>3</v>
       </c>
       <c r="D7" t="s">
-        <v>266</v>
+        <v>1595</v>
       </c>
       <c r="E7" t="str">
         <f t="shared" si="0"/>
-        <v>Exeggutor 3</v>
+        <v>Persian 3</v>
       </c>
       <c r="F7">
         <f>IF(AND(A7&lt;&gt;"",ISNUMBER(C7),D7&lt;&gt;""),_xlfn.XLOOKUP(A7,'Table of IDs'!M:M,'Table of IDs'!L:L),"")</f>
-        <v>103</v>
+        <v>53</v>
       </c>
       <c r="G7" t="str">
-        <f t="shared" si="3"/>
-        <v>0067</v>
+        <f t="shared" si="1"/>
+        <v>0035</v>
       </c>
       <c r="H7" t="str" cm="1">
         <f t="array" ref="H7">IF(G7&lt;&gt;"",RIGHT(G7,2)&amp;LEFT(G7,2)&amp;_xlfn.XLOOKUP(D7,'Table of IDs'!$C:C,'Table of IDs'!D:D)&amp;DEC2HEX(C7,2)&amp;DEC2HEX(B7,2),"")</f>
-        <v>67009B0303FF</v>
+        <v>3500470103FF</v>
       </c>
       <c r="I7" t="str">
-        <f t="shared" si="4"/>
-        <v>670003</v>
+        <f t="shared" si="2"/>
+        <v>350003</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>384</v>
+        <v>143</v>
       </c>
       <c r="B8">
         <v>255</v>
       </c>
       <c r="C8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8" t="s">
-        <v>1527</v>
+        <v>266</v>
       </c>
       <c r="E8" t="str">
         <f t="shared" si="0"/>
-        <v>Marowak 2</v>
+        <v>Persian 3</v>
       </c>
       <c r="F8">
         <f>IF(AND(A8&lt;&gt;"",ISNUMBER(C8),D8&lt;&gt;""),_xlfn.XLOOKUP(A8,'Table of IDs'!M:M,'Table of IDs'!L:L),"")</f>
-        <v>105</v>
+        <v>53</v>
       </c>
       <c r="G8" t="str">
-        <f t="shared" si="3"/>
-        <v>0069</v>
+        <f t="shared" si="1"/>
+        <v>0035</v>
       </c>
       <c r="H8" t="str" cm="1">
         <f t="array" ref="H8">IF(G8&lt;&gt;"",RIGHT(G8,2)&amp;LEFT(G8,2)&amp;_xlfn.XLOOKUP(D8,'Table of IDs'!$C:C,'Table of IDs'!D:D)&amp;DEC2HEX(C8,2)&amp;DEC2HEX(B8,2),"")</f>
-        <v>6900020102FF</v>
+        <v>35009B0303FF</v>
       </c>
       <c r="I8" t="str">
-        <f t="shared" si="4"/>
-        <v>690002</v>
+        <f t="shared" si="2"/>
+        <v/>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>384</v>
+        <v>150</v>
       </c>
       <c r="B9">
         <v>255</v>
@@ -7983,202 +8055,202 @@
         <v>2</v>
       </c>
       <c r="D9" t="s">
-        <v>266</v>
+        <v>1910</v>
       </c>
       <c r="E9" t="str">
         <f t="shared" si="0"/>
-        <v>Marowak 2</v>
+        <v>Slowbro 2</v>
       </c>
       <c r="F9">
         <f>IF(AND(A9&lt;&gt;"",ISNUMBER(C9),D9&lt;&gt;""),_xlfn.XLOOKUP(A9,'Table of IDs'!M:M,'Table of IDs'!L:L),"")</f>
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="G9" t="str">
-        <f t="shared" si="3"/>
-        <v>0069</v>
+        <f t="shared" si="1"/>
+        <v>0050</v>
       </c>
       <c r="H9" t="str" cm="1">
         <f t="array" ref="H9">IF(G9&lt;&gt;"",RIGHT(G9,2)&amp;LEFT(G9,2)&amp;_xlfn.XLOOKUP(D9,'Table of IDs'!$C:C,'Table of IDs'!D:D)&amp;DEC2HEX(C9,2)&amp;DEC2HEX(B9,2),"")</f>
-        <v>69009B0302FF</v>
+        <v>5000F80202FF</v>
       </c>
       <c r="I9" t="str">
-        <f t="shared" si="4"/>
-        <v/>
+        <f t="shared" si="2"/>
+        <v>500002</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" t="s">
-        <v>422</v>
+        <v>382</v>
       </c>
       <c r="B10">
         <v>255</v>
       </c>
       <c r="C10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D10" t="s">
-        <v>246</v>
+        <v>266</v>
       </c>
       <c r="E10" t="str">
         <f t="shared" si="0"/>
-        <v>Snorlax 1</v>
+        <v>Exeggutor 3</v>
       </c>
       <c r="F10">
         <f>IF(AND(A10&lt;&gt;"",ISNUMBER(C10),D10&lt;&gt;""),_xlfn.XLOOKUP(A10,'Table of IDs'!M:M,'Table of IDs'!L:L),"")</f>
-        <v>143</v>
+        <v>103</v>
       </c>
       <c r="G10" t="str">
-        <f t="shared" si="3"/>
-        <v>008F</v>
+        <f t="shared" si="1"/>
+        <v>0067</v>
       </c>
       <c r="H10" t="str" cm="1">
         <f t="array" ref="H10">IF(G10&lt;&gt;"",RIGHT(G10,2)&amp;LEFT(G10,2)&amp;_xlfn.XLOOKUP(D10,'Table of IDs'!$C:C,'Table of IDs'!D:D)&amp;DEC2HEX(C10,2)&amp;DEC2HEX(B10,2),"")</f>
-        <v>8F00240301FF</v>
+        <v>67009B0303FF</v>
       </c>
       <c r="I10" t="str">
-        <f t="shared" si="4"/>
-        <v>8F0001</v>
+        <f t="shared" si="2"/>
+        <v>670003</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" t="s">
-        <v>422</v>
+        <v>384</v>
       </c>
       <c r="B11">
         <v>255</v>
       </c>
       <c r="C11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" t="s">
-        <v>2132</v>
+        <v>1527</v>
       </c>
       <c r="E11" t="str">
-        <f t="shared" ref="E11:E16" si="5">_xlfn.CONCAT(A11," ",C11)</f>
-        <v>Snorlax 1</v>
+        <f t="shared" si="0"/>
+        <v>Marowak 2</v>
       </c>
       <c r="F11">
         <f>IF(AND(A11&lt;&gt;"",ISNUMBER(C11),D11&lt;&gt;""),_xlfn.XLOOKUP(A11,'Table of IDs'!M:M,'Table of IDs'!L:L),"")</f>
-        <v>143</v>
+        <v>105</v>
       </c>
       <c r="G11" t="str">
-        <f t="shared" si="3"/>
-        <v>008F</v>
+        <f t="shared" si="1"/>
+        <v>0069</v>
       </c>
       <c r="H11" t="str" cm="1">
         <f t="array" ref="H11">IF(G11&lt;&gt;"",RIGHT(G11,2)&amp;LEFT(G11,2)&amp;_xlfn.XLOOKUP(D11,'Table of IDs'!$C:C,'Table of IDs'!D:D)&amp;DEC2HEX(C11,2)&amp;DEC2HEX(B11,2),"")</f>
-        <v>8F005D0301FF</v>
+        <v>6900020102FF</v>
       </c>
       <c r="I11" t="str">
-        <f t="shared" si="4"/>
-        <v/>
+        <f t="shared" si="2"/>
+        <v>690002</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" t="s">
-        <v>146</v>
+        <v>384</v>
       </c>
       <c r="B12">
         <v>255</v>
       </c>
       <c r="C12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D12" t="s">
-        <v>1832</v>
+        <v>266</v>
       </c>
       <c r="E12" t="str">
-        <f t="shared" ref="E12" si="6">_xlfn.CONCAT(A12," ",C12)</f>
-        <v>Scizor 3</v>
+        <f t="shared" si="0"/>
+        <v>Marowak 2</v>
       </c>
       <c r="F12">
         <f>IF(AND(A12&lt;&gt;"",ISNUMBER(C12),D12&lt;&gt;""),_xlfn.XLOOKUP(A12,'Table of IDs'!M:M,'Table of IDs'!L:L),"")</f>
-        <v>212</v>
+        <v>105</v>
       </c>
       <c r="G12" t="str">
-        <f t="shared" si="3"/>
-        <v>00D4</v>
+        <f t="shared" si="1"/>
+        <v>0069</v>
       </c>
       <c r="H12" t="str" cm="1">
         <f t="array" ref="H12">IF(G12&lt;&gt;"",RIGHT(G12,2)&amp;LEFT(G12,2)&amp;_xlfn.XLOOKUP(D12,'Table of IDs'!$C:C,'Table of IDs'!D:D)&amp;DEC2HEX(C12,2)&amp;DEC2HEX(B12,2),"")</f>
-        <v>D4009E0203FF</v>
+        <v>69009B0302FF</v>
       </c>
       <c r="I12" t="str">
-        <f t="shared" si="4"/>
-        <v>D40003</v>
+        <f t="shared" si="2"/>
+        <v/>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" t="s">
-        <v>146</v>
+        <v>422</v>
       </c>
       <c r="B13">
         <v>255</v>
       </c>
       <c r="C13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D13" t="s">
-        <v>266</v>
+        <v>246</v>
       </c>
       <c r="E13" t="str">
-        <f t="shared" si="5"/>
-        <v>Scizor 3</v>
+        <f t="shared" si="0"/>
+        <v>Snorlax 1</v>
       </c>
       <c r="F13">
         <f>IF(AND(A13&lt;&gt;"",ISNUMBER(C13),D13&lt;&gt;""),_xlfn.XLOOKUP(A13,'Table of IDs'!M:M,'Table of IDs'!L:L),"")</f>
-        <v>212</v>
+        <v>143</v>
       </c>
       <c r="G13" t="str">
-        <f t="shared" si="3"/>
-        <v>00D4</v>
+        <f t="shared" si="1"/>
+        <v>008F</v>
       </c>
       <c r="H13" t="str" cm="1">
         <f t="array" ref="H13">IF(G13&lt;&gt;"",RIGHT(G13,2)&amp;LEFT(G13,2)&amp;_xlfn.XLOOKUP(D13,'Table of IDs'!$C:C,'Table of IDs'!D:D)&amp;DEC2HEX(C13,2)&amp;DEC2HEX(B13,2),"")</f>
-        <v>D4009B0303FF</v>
+        <v>8F00240301FF</v>
       </c>
       <c r="I13" t="str">
-        <f t="shared" si="4"/>
-        <v/>
+        <f t="shared" si="2"/>
+        <v>8F0001</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" t="s">
-        <v>439</v>
+        <v>422</v>
       </c>
       <c r="B14">
         <v>255</v>
       </c>
       <c r="C14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D14" t="s">
-        <v>2291</v>
+        <v>2131</v>
       </c>
       <c r="E14" t="str">
-        <f t="shared" si="5"/>
-        <v>Feraligatr 2</v>
+        <f t="shared" ref="E14:E27" si="3">_xlfn.CONCAT(A14," ",C14)</f>
+        <v>Snorlax 1</v>
       </c>
       <c r="F14">
         <f>IF(AND(A14&lt;&gt;"",ISNUMBER(C14),D14&lt;&gt;""),_xlfn.XLOOKUP(A14,'Table of IDs'!M:M,'Table of IDs'!L:L),"")</f>
-        <v>160</v>
+        <v>143</v>
       </c>
       <c r="G14" t="str">
-        <f t="shared" si="3"/>
-        <v>00A0</v>
+        <f t="shared" ref="G14:G27" si="4">IF(F14&lt;&gt;"",DEC2HEX(F14,4),"")</f>
+        <v>008F</v>
       </c>
       <c r="H14" t="str" cm="1">
         <f t="array" ref="H14">IF(G14&lt;&gt;"",RIGHT(G14,2)&amp;LEFT(G14,2)&amp;_xlfn.XLOOKUP(D14,'Table of IDs'!$C:C,'Table of IDs'!D:D)&amp;DEC2HEX(C14,2)&amp;DEC2HEX(B14,2),"")</f>
-        <v>A000640302FF</v>
+        <v>8F005D0301FF</v>
       </c>
       <c r="I14" t="str">
-        <f t="shared" si="4"/>
-        <v>A00002</v>
+        <f t="shared" ref="I14:I27" si="5">IF(OR(A14&lt;&gt;A13,C14&lt;&gt;C13),LEFT(H14,4)&amp;LEFT(RIGHT(H14,4),2),"")</f>
+        <v/>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B15">
         <v>255</v>
@@ -8187,66 +8259,66 @@
         <v>3</v>
       </c>
       <c r="D15" t="s">
-        <v>266</v>
+        <v>1832</v>
       </c>
       <c r="E15" t="str">
-        <f t="shared" si="5"/>
-        <v>Donphan 3</v>
+        <f t="shared" si="3"/>
+        <v>Scizor 3</v>
       </c>
       <c r="F15">
         <f>IF(AND(A15&lt;&gt;"",ISNUMBER(C15),D15&lt;&gt;""),_xlfn.XLOOKUP(A15,'Table of IDs'!M:M,'Table of IDs'!L:L),"")</f>
-        <v>232</v>
+        <v>212</v>
       </c>
       <c r="G15" t="str">
-        <f t="shared" si="3"/>
-        <v>00E8</v>
+        <f t="shared" si="4"/>
+        <v>00D4</v>
       </c>
       <c r="H15" t="str" cm="1">
         <f t="array" ref="H15">IF(G15&lt;&gt;"",RIGHT(G15,2)&amp;LEFT(G15,2)&amp;_xlfn.XLOOKUP(D15,'Table of IDs'!$C:C,'Table of IDs'!D:D)&amp;DEC2HEX(C15,2)&amp;DEC2HEX(B15,2),"")</f>
-        <v>E8009B0303FF</v>
+        <v>D4009E0203FF</v>
       </c>
       <c r="I15" t="str">
-        <f t="shared" si="4"/>
-        <v>E80003</v>
+        <f t="shared" si="5"/>
+        <v>D40003</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B16">
         <v>255</v>
       </c>
       <c r="C16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D16" t="s">
-        <v>1831</v>
+        <v>266</v>
       </c>
       <c r="E16" t="str">
-        <f t="shared" si="5"/>
-        <v>Tyranitar 2</v>
+        <f t="shared" si="3"/>
+        <v>Scizor 3</v>
       </c>
       <c r="F16">
         <f>IF(AND(A16&lt;&gt;"",ISNUMBER(C16),D16&lt;&gt;""),_xlfn.XLOOKUP(A16,'Table of IDs'!M:M,'Table of IDs'!L:L),"")</f>
-        <v>248</v>
+        <v>212</v>
       </c>
       <c r="G16" t="str">
-        <f t="shared" si="3"/>
-        <v>00F8</v>
+        <f t="shared" si="4"/>
+        <v>00D4</v>
       </c>
       <c r="H16" t="str" cm="1">
         <f t="array" ref="H16">IF(G16&lt;&gt;"",RIGHT(G16,2)&amp;LEFT(G16,2)&amp;_xlfn.XLOOKUP(D16,'Table of IDs'!$C:C,'Table of IDs'!D:D)&amp;DEC2HEX(C16,2)&amp;DEC2HEX(B16,2),"")</f>
-        <v>F8009D0202FF</v>
+        <v>D4009B0303FF</v>
       </c>
       <c r="I16" t="str">
-        <f t="shared" si="4"/>
-        <v>F80002</v>
+        <f t="shared" si="5"/>
+        <v/>
       </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" t="s">
-        <v>151</v>
+        <v>433</v>
       </c>
       <c r="B17">
         <v>255</v>
@@ -8255,168 +8327,168 @@
         <v>2</v>
       </c>
       <c r="D17" t="s">
-        <v>1919</v>
+        <v>2296</v>
       </c>
       <c r="E17" t="str">
-        <f t="shared" ref="E17:E18" si="7">_xlfn.CONCAT(A17," ",C17)</f>
-        <v>Salamence 2</v>
+        <f t="shared" si="3"/>
+        <v>Meganium 2</v>
       </c>
       <c r="F17">
         <f>IF(AND(A17&lt;&gt;"",ISNUMBER(C17),D17&lt;&gt;""),_xlfn.XLOOKUP(A17,'Table of IDs'!M:M,'Table of IDs'!L:L),"")</f>
-        <v>373</v>
+        <v>154</v>
       </c>
       <c r="G17" t="str">
-        <f t="shared" si="3"/>
-        <v>0175</v>
+        <f t="shared" ref="G17:G19" si="6">IF(F17&lt;&gt;"",DEC2HEX(F17,4),"")</f>
+        <v>009A</v>
       </c>
       <c r="H17" t="str" cm="1">
         <f t="array" ref="H17">IF(G17&lt;&gt;"",RIGHT(G17,2)&amp;LEFT(G17,2)&amp;_xlfn.XLOOKUP(D17,'Table of IDs'!$C:C,'Table of IDs'!D:D)&amp;DEC2HEX(C17,2)&amp;DEC2HEX(B17,2),"")</f>
-        <v>7501010302FF</v>
+        <v>9A00680302FF</v>
       </c>
       <c r="I17" t="str">
-        <f t="shared" si="4"/>
-        <v>750102</v>
+        <f t="shared" ref="I17:I19" si="7">IF(OR(A17&lt;&gt;A16,C17&lt;&gt;C16),LEFT(H17,4)&amp;LEFT(RIGHT(H17,4),2),"")</f>
+        <v>9A0002</v>
       </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" t="s">
-        <v>654</v>
+        <v>439</v>
       </c>
       <c r="B18">
-        <v>0</v>
+        <v>255</v>
       </c>
       <c r="C18">
         <v>2</v>
       </c>
       <c r="D18" t="s">
-        <v>1846</v>
+        <v>2290</v>
       </c>
       <c r="E18" t="str">
-        <f t="shared" si="7"/>
-        <v>Latias 2</v>
+        <f t="shared" si="3"/>
+        <v>Feraligatr 2</v>
       </c>
       <c r="F18">
         <f>IF(AND(A18&lt;&gt;"",ISNUMBER(C18),D18&lt;&gt;""),_xlfn.XLOOKUP(A18,'Table of IDs'!M:M,'Table of IDs'!L:L),"")</f>
-        <v>380</v>
+        <v>160</v>
       </c>
       <c r="G18" t="str">
-        <f t="shared" si="3"/>
-        <v>017C</v>
+        <f t="shared" si="6"/>
+        <v>00A0</v>
       </c>
       <c r="H18" t="str" cm="1">
         <f t="array" ref="H18">IF(G18&lt;&gt;"",RIGHT(G18,2)&amp;LEFT(G18,2)&amp;_xlfn.XLOOKUP(D18,'Table of IDs'!$C:C,'Table of IDs'!D:D)&amp;DEC2HEX(C18,2)&amp;DEC2HEX(B18,2),"")</f>
-        <v>7C01AC020200</v>
+        <v>A000640302FF</v>
       </c>
       <c r="I18" t="str">
-        <f t="shared" si="4"/>
-        <v>7C0102</v>
+        <f t="shared" si="7"/>
+        <v>A00002</v>
       </c>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" t="s">
-        <v>654</v>
+        <v>147</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>255</v>
       </c>
       <c r="C19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D19" t="s">
-        <v>1494</v>
+        <v>266</v>
       </c>
       <c r="E19" t="str">
-        <f t="shared" ref="E19:E26" si="8">_xlfn.CONCAT(A19," ",C19)</f>
-        <v>Latias 2</v>
+        <f t="shared" si="3"/>
+        <v>Donphan 3</v>
       </c>
       <c r="F19">
         <f>IF(AND(A19&lt;&gt;"",ISNUMBER(C19),D19&lt;&gt;""),_xlfn.XLOOKUP(A19,'Table of IDs'!M:M,'Table of IDs'!L:L),"")</f>
-        <v>380</v>
+        <v>232</v>
       </c>
       <c r="G19" t="str">
-        <f t="shared" si="3"/>
-        <v>017C</v>
+        <f t="shared" si="6"/>
+        <v>00E8</v>
       </c>
       <c r="H19" t="str" cm="1">
         <f t="array" ref="H19">IF(G19&lt;&gt;"",RIGHT(G19,2)&amp;LEFT(G19,2)&amp;_xlfn.XLOOKUP(D19,'Table of IDs'!$C:C,'Table of IDs'!D:D)&amp;DEC2HEX(C19,2)&amp;DEC2HEX(B19,2),"")</f>
-        <v>7C01E1000200</v>
+        <v>E8009B0303FF</v>
       </c>
       <c r="I19" t="str">
-        <f t="shared" si="4"/>
-        <v/>
+        <f t="shared" si="7"/>
+        <v>E80003</v>
       </c>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" t="s">
-        <v>654</v>
+        <v>149</v>
       </c>
       <c r="B20">
-        <v>1</v>
+        <v>255</v>
       </c>
       <c r="C20">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D20" t="s">
-        <v>1846</v>
+        <v>1831</v>
       </c>
       <c r="E20" t="str">
-        <f t="shared" si="8"/>
-        <v>Latias 3</v>
+        <f t="shared" si="3"/>
+        <v>Tyranitar 2</v>
       </c>
       <c r="F20">
         <f>IF(AND(A20&lt;&gt;"",ISNUMBER(C20),D20&lt;&gt;""),_xlfn.XLOOKUP(A20,'Table of IDs'!M:M,'Table of IDs'!L:L),"")</f>
-        <v>380</v>
+        <v>248</v>
       </c>
       <c r="G20" t="str">
-        <f t="shared" si="3"/>
-        <v>017C</v>
+        <f t="shared" si="4"/>
+        <v>00F8</v>
       </c>
       <c r="H20" t="str" cm="1">
         <f t="array" ref="H20">IF(G20&lt;&gt;"",RIGHT(G20,2)&amp;LEFT(G20,2)&amp;_xlfn.XLOOKUP(D20,'Table of IDs'!$C:C,'Table of IDs'!D:D)&amp;DEC2HEX(C20,2)&amp;DEC2HEX(B20,2),"")</f>
-        <v>7C01AC020301</v>
+        <v>F8009D0202FF</v>
       </c>
       <c r="I20" t="str">
-        <f t="shared" si="4"/>
-        <v>7C0103</v>
+        <f t="shared" si="5"/>
+        <v>F80002</v>
       </c>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" t="s">
-        <v>654</v>
+        <v>151</v>
       </c>
       <c r="B21">
-        <v>1</v>
+        <v>255</v>
       </c>
       <c r="C21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D21" t="s">
-        <v>1494</v>
+        <v>1919</v>
       </c>
       <c r="E21" t="str">
-        <f t="shared" si="8"/>
-        <v>Latias 3</v>
+        <f t="shared" si="3"/>
+        <v>Salamence 2</v>
       </c>
       <c r="F21">
         <f>IF(AND(A21&lt;&gt;"",ISNUMBER(C21),D21&lt;&gt;""),_xlfn.XLOOKUP(A21,'Table of IDs'!M:M,'Table of IDs'!L:L),"")</f>
-        <v>380</v>
+        <v>373</v>
       </c>
       <c r="G21" t="str">
-        <f t="shared" si="3"/>
-        <v>017C</v>
+        <f t="shared" si="4"/>
+        <v>0175</v>
       </c>
       <c r="H21" t="str" cm="1">
         <f t="array" ref="H21">IF(G21&lt;&gt;"",RIGHT(G21,2)&amp;LEFT(G21,2)&amp;_xlfn.XLOOKUP(D21,'Table of IDs'!$C:C,'Table of IDs'!D:D)&amp;DEC2HEX(C21,2)&amp;DEC2HEX(B21,2),"")</f>
-        <v>7C01E1000301</v>
+        <v>7501010302FF</v>
       </c>
       <c r="I21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
+        <f t="shared" si="5"/>
+        <v>750102</v>
       </c>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -8425,32 +8497,32 @@
         <v>2</v>
       </c>
       <c r="D22" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="E22" t="str">
-        <f t="shared" si="8"/>
-        <v>Latios 2</v>
+        <f t="shared" si="3"/>
+        <v>Latias 2</v>
       </c>
       <c r="F22">
         <f>IF(AND(A22&lt;&gt;"",ISNUMBER(C22),D22&lt;&gt;""),_xlfn.XLOOKUP(A22,'Table of IDs'!M:M,'Table of IDs'!L:L),"")</f>
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="G22" t="str">
-        <f t="shared" si="3"/>
-        <v>017D</v>
+        <f t="shared" si="4"/>
+        <v>017C</v>
       </c>
       <c r="H22" t="str" cm="1">
         <f t="array" ref="H22">IF(G22&lt;&gt;"",RIGHT(G22,2)&amp;LEFT(G22,2)&amp;_xlfn.XLOOKUP(D22,'Table of IDs'!$C:C,'Table of IDs'!D:D)&amp;DEC2HEX(C22,2)&amp;DEC2HEX(B22,2),"")</f>
-        <v>7D01AD020200</v>
+        <v>7C01AC020200</v>
       </c>
       <c r="I22" t="str">
-        <f t="shared" si="4"/>
-        <v>7D0102</v>
+        <f t="shared" si="5"/>
+        <v>7C0102</v>
       </c>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -8462,29 +8534,29 @@
         <v>1494</v>
       </c>
       <c r="E23" t="str">
-        <f t="shared" si="8"/>
-        <v>Latios 2</v>
+        <f t="shared" si="3"/>
+        <v>Latias 2</v>
       </c>
       <c r="F23">
         <f>IF(AND(A23&lt;&gt;"",ISNUMBER(C23),D23&lt;&gt;""),_xlfn.XLOOKUP(A23,'Table of IDs'!M:M,'Table of IDs'!L:L),"")</f>
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="G23" t="str">
-        <f t="shared" si="3"/>
-        <v>017D</v>
+        <f t="shared" si="4"/>
+        <v>017C</v>
       </c>
       <c r="H23" t="str" cm="1">
         <f t="array" ref="H23">IF(G23&lt;&gt;"",RIGHT(G23,2)&amp;LEFT(G23,2)&amp;_xlfn.XLOOKUP(D23,'Table of IDs'!$C:C,'Table of IDs'!D:D)&amp;DEC2HEX(C23,2)&amp;DEC2HEX(B23,2),"")</f>
-        <v>7D01E1000200</v>
+        <v>7C01E1000200</v>
       </c>
       <c r="I23" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B24">
         <v>1</v>
@@ -8493,406 +8565,406 @@
         <v>3</v>
       </c>
       <c r="D24" t="s">
+        <v>1846</v>
+      </c>
+      <c r="E24" t="str">
+        <f t="shared" si="3"/>
+        <v>Latias 3</v>
+      </c>
+      <c r="F24">
+        <f>IF(AND(A24&lt;&gt;"",ISNUMBER(C24),D24&lt;&gt;""),_xlfn.XLOOKUP(A24,'Table of IDs'!M:M,'Table of IDs'!L:L),"")</f>
+        <v>380</v>
+      </c>
+      <c r="G24" t="str">
+        <f t="shared" si="4"/>
+        <v>017C</v>
+      </c>
+      <c r="H24" t="str" cm="1">
+        <f t="array" ref="H24">IF(G24&lt;&gt;"",RIGHT(G24,2)&amp;LEFT(G24,2)&amp;_xlfn.XLOOKUP(D24,'Table of IDs'!$C:C,'Table of IDs'!D:D)&amp;DEC2HEX(C24,2)&amp;DEC2HEX(B24,2),"")</f>
+        <v>7C01AC020301</v>
+      </c>
+      <c r="I24" t="str">
+        <f t="shared" si="5"/>
+        <v>7C0103</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" t="s">
+        <v>654</v>
+      </c>
+      <c r="B25">
+        <v>1</v>
+      </c>
+      <c r="C25">
+        <v>3</v>
+      </c>
+      <c r="D25" t="s">
+        <v>1494</v>
+      </c>
+      <c r="E25" t="str">
+        <f t="shared" si="3"/>
+        <v>Latias 3</v>
+      </c>
+      <c r="F25">
+        <f>IF(AND(A25&lt;&gt;"",ISNUMBER(C25),D25&lt;&gt;""),_xlfn.XLOOKUP(A25,'Table of IDs'!M:M,'Table of IDs'!L:L),"")</f>
+        <v>380</v>
+      </c>
+      <c r="G25" t="str">
+        <f t="shared" si="4"/>
+        <v>017C</v>
+      </c>
+      <c r="H25" t="str" cm="1">
+        <f t="array" ref="H25">IF(G25&lt;&gt;"",RIGHT(G25,2)&amp;LEFT(G25,2)&amp;_xlfn.XLOOKUP(D25,'Table of IDs'!$C:C,'Table of IDs'!D:D)&amp;DEC2HEX(C25,2)&amp;DEC2HEX(B25,2),"")</f>
+        <v>7C01E1000301</v>
+      </c>
+      <c r="I25" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" t="s">
+        <v>655</v>
+      </c>
+      <c r="B26">
+        <v>0</v>
+      </c>
+      <c r="C26">
+        <v>2</v>
+      </c>
+      <c r="D26" t="s">
         <v>1847</v>
       </c>
-      <c r="E24" t="str">
+      <c r="E26" t="str">
+        <f t="shared" si="3"/>
+        <v>Latios 2</v>
+      </c>
+      <c r="F26">
+        <f>IF(AND(A26&lt;&gt;"",ISNUMBER(C26),D26&lt;&gt;""),_xlfn.XLOOKUP(A26,'Table of IDs'!M:M,'Table of IDs'!L:L),"")</f>
+        <v>381</v>
+      </c>
+      <c r="G26" t="str">
+        <f t="shared" si="4"/>
+        <v>017D</v>
+      </c>
+      <c r="H26" t="str" cm="1">
+        <f t="array" ref="H26">IF(G26&lt;&gt;"",RIGHT(G26,2)&amp;LEFT(G26,2)&amp;_xlfn.XLOOKUP(D26,'Table of IDs'!$C:C,'Table of IDs'!D:D)&amp;DEC2HEX(C26,2)&amp;DEC2HEX(B26,2),"")</f>
+        <v>7D01AD020200</v>
+      </c>
+      <c r="I26" t="str">
+        <f t="shared" si="5"/>
+        <v>7D0102</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" t="s">
+        <v>655</v>
+      </c>
+      <c r="B27">
+        <v>0</v>
+      </c>
+      <c r="C27">
+        <v>2</v>
+      </c>
+      <c r="D27" t="s">
+        <v>1494</v>
+      </c>
+      <c r="E27" t="str">
+        <f t="shared" si="3"/>
+        <v>Latios 2</v>
+      </c>
+      <c r="F27">
+        <f>IF(AND(A27&lt;&gt;"",ISNUMBER(C27),D27&lt;&gt;""),_xlfn.XLOOKUP(A27,'Table of IDs'!M:M,'Table of IDs'!L:L),"")</f>
+        <v>381</v>
+      </c>
+      <c r="G27" t="str">
+        <f t="shared" si="4"/>
+        <v>017D</v>
+      </c>
+      <c r="H27" t="str" cm="1">
+        <f t="array" ref="H27">IF(G27&lt;&gt;"",RIGHT(G27,2)&amp;LEFT(G27,2)&amp;_xlfn.XLOOKUP(D27,'Table of IDs'!$C:C,'Table of IDs'!D:D)&amp;DEC2HEX(C27,2)&amp;DEC2HEX(B27,2),"")</f>
+        <v>7D01E1000200</v>
+      </c>
+      <c r="I27" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" t="s">
+        <v>655</v>
+      </c>
+      <c r="B28">
+        <v>1</v>
+      </c>
+      <c r="C28">
+        <v>3</v>
+      </c>
+      <c r="D28" t="s">
+        <v>1847</v>
+      </c>
+      <c r="E28" t="str">
+        <f t="shared" ref="E28:E60" si="8">_xlfn.CONCAT(A28," ",C28)</f>
+        <v>Latios 3</v>
+      </c>
+      <c r="F28">
+        <f>IF(AND(A28&lt;&gt;"",ISNUMBER(C28),D28&lt;&gt;""),_xlfn.XLOOKUP(A28,'Table of IDs'!M:M,'Table of IDs'!L:L),"")</f>
+        <v>381</v>
+      </c>
+      <c r="G28" t="str">
+        <f t="shared" ref="G28:G60" si="9">IF(F28&lt;&gt;"",DEC2HEX(F28,4),"")</f>
+        <v>017D</v>
+      </c>
+      <c r="H28" t="str" cm="1">
+        <f t="array" ref="H28">IF(G28&lt;&gt;"",RIGHT(G28,2)&amp;LEFT(G28,2)&amp;_xlfn.XLOOKUP(D28,'Table of IDs'!$C:C,'Table of IDs'!D:D)&amp;DEC2HEX(C28,2)&amp;DEC2HEX(B28,2),"")</f>
+        <v>7D01AD020301</v>
+      </c>
+      <c r="I28" t="str">
+        <f t="shared" ref="I28:I60" si="10">IF(OR(A28&lt;&gt;A27,C28&lt;&gt;C27),LEFT(H28,4)&amp;LEFT(RIGHT(H28,4),2),"")</f>
+        <v>7D0103</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29" t="s">
+        <v>655</v>
+      </c>
+      <c r="B29">
+        <v>1</v>
+      </c>
+      <c r="C29">
+        <v>3</v>
+      </c>
+      <c r="D29" t="s">
+        <v>1494</v>
+      </c>
+      <c r="E29" t="str">
         <f t="shared" si="8"/>
         <v>Latios 3</v>
       </c>
-      <c r="F24">
-        <f>IF(AND(A24&lt;&gt;"",ISNUMBER(C24),D24&lt;&gt;""),_xlfn.XLOOKUP(A24,'Table of IDs'!M:M,'Table of IDs'!L:L),"")</f>
+      <c r="F29">
+        <f>IF(AND(A29&lt;&gt;"",ISNUMBER(C29),D29&lt;&gt;""),_xlfn.XLOOKUP(A29,'Table of IDs'!M:M,'Table of IDs'!L:L),"")</f>
         <v>381</v>
       </c>
-      <c r="G24" t="str">
-        <f t="shared" si="3"/>
+      <c r="G29" t="str">
+        <f t="shared" si="9"/>
         <v>017D</v>
       </c>
-      <c r="H24" t="str" cm="1">
-        <f t="array" ref="H24">IF(G24&lt;&gt;"",RIGHT(G24,2)&amp;LEFT(G24,2)&amp;_xlfn.XLOOKUP(D24,'Table of IDs'!$C:C,'Table of IDs'!D:D)&amp;DEC2HEX(C24,2)&amp;DEC2HEX(B24,2),"")</f>
-        <v>7D01AD020301</v>
-      </c>
-      <c r="I24" t="str">
-        <f t="shared" si="4"/>
-        <v>7D0103</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9">
-      <c r="A25" t="s">
-        <v>655</v>
-      </c>
-      <c r="B25">
-        <v>1</v>
-      </c>
-      <c r="C25">
-        <v>3</v>
-      </c>
-      <c r="D25" t="s">
-        <v>1494</v>
-      </c>
-      <c r="E25" t="str">
-        <f t="shared" si="8"/>
-        <v>Latios 3</v>
-      </c>
-      <c r="F25">
-        <f>IF(AND(A25&lt;&gt;"",ISNUMBER(C25),D25&lt;&gt;""),_xlfn.XLOOKUP(A25,'Table of IDs'!M:M,'Table of IDs'!L:L),"")</f>
-        <v>381</v>
-      </c>
-      <c r="G25" t="str">
-        <f t="shared" si="3"/>
-        <v>017D</v>
-      </c>
-      <c r="H25" t="str" cm="1">
-        <f t="array" ref="H25">IF(G25&lt;&gt;"",RIGHT(G25,2)&amp;LEFT(G25,2)&amp;_xlfn.XLOOKUP(D25,'Table of IDs'!$C:C,'Table of IDs'!D:D)&amp;DEC2HEX(C25,2)&amp;DEC2HEX(B25,2),"")</f>
+      <c r="H29" t="str" cm="1">
+        <f t="array" ref="H29">IF(G29&lt;&gt;"",RIGHT(G29,2)&amp;LEFT(G29,2)&amp;_xlfn.XLOOKUP(D29,'Table of IDs'!$C:C,'Table of IDs'!D:D)&amp;DEC2HEX(C29,2)&amp;DEC2HEX(B29,2),"")</f>
         <v>7D01E1000301</v>
       </c>
-      <c r="I25" t="str">
-        <f t="shared" si="4"/>
+      <c r="I29" t="str">
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:9">
-      <c r="A26" t="s">
+    <row r="30" spans="1:9">
+      <c r="A30" t="s">
         <v>747</v>
       </c>
-      <c r="B26">
+      <c r="B30">
         <v>255</v>
       </c>
-      <c r="C26">
+      <c r="C30">
         <v>2</v>
       </c>
-      <c r="D26" t="s">
+      <c r="D30" t="s">
         <v>259</v>
       </c>
-      <c r="E26" t="str">
+      <c r="E30" t="str">
         <f t="shared" si="8"/>
         <v>Porygon-Z 2</v>
       </c>
-      <c r="F26">
-        <f>IF(AND(A26&lt;&gt;"",ISNUMBER(C26),D26&lt;&gt;""),_xlfn.XLOOKUP(A26,'Table of IDs'!M:M,'Table of IDs'!L:L),"")</f>
-        <v>474</v>
-      </c>
-      <c r="G26" t="str">
-        <f t="shared" si="3"/>
-        <v>01DA</v>
-      </c>
-      <c r="H26" t="str" cm="1">
-        <f t="array" ref="H26">IF(G26&lt;&gt;"",RIGHT(G26,2)&amp;LEFT(G26,2)&amp;_xlfn.XLOOKUP(D26,'Table of IDs'!$C:C,'Table of IDs'!D:D)&amp;DEC2HEX(C26,2)&amp;DEC2HEX(B26,2),"")</f>
-        <v>DA01160302FF</v>
-      </c>
-      <c r="I26" t="str">
-        <f t="shared" si="4"/>
-        <v>DA0102</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9">
-      <c r="A27" t="s">
-        <v>747</v>
-      </c>
-      <c r="B27">
-        <v>255</v>
-      </c>
-      <c r="C27">
-        <v>2</v>
-      </c>
-      <c r="D27" t="s">
-        <v>1285</v>
-      </c>
-      <c r="E27" t="str">
-        <f t="shared" ref="E27:E52" si="9">_xlfn.CONCAT(A27," ",C27)</f>
-        <v>Porygon-Z 2</v>
-      </c>
-      <c r="F27">
-        <f>IF(AND(A27&lt;&gt;"",ISNUMBER(C27),D27&lt;&gt;""),_xlfn.XLOOKUP(A27,'Table of IDs'!M:M,'Table of IDs'!L:L),"")</f>
-        <v>474</v>
-      </c>
-      <c r="G27" t="str">
-        <f t="shared" si="3"/>
-        <v>01DA</v>
-      </c>
-      <c r="H27" t="str" cm="1">
-        <f t="array" ref="H27">IF(G27&lt;&gt;"",RIGHT(G27,2)&amp;LEFT(G27,2)&amp;_xlfn.XLOOKUP(D27,'Table of IDs'!$C:C,'Table of IDs'!D:D)&amp;DEC2HEX(C27,2)&amp;DEC2HEX(B27,2),"")</f>
-        <v>DA010E0102FF</v>
-      </c>
-      <c r="I27" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="28" spans="1:9">
-      <c r="A28" t="s">
-        <v>882</v>
-      </c>
-      <c r="B28">
-        <v>255</v>
-      </c>
-      <c r="C28">
-        <v>2</v>
-      </c>
-      <c r="D28" t="s">
-        <v>2288</v>
-      </c>
-      <c r="E28" t="str">
-        <f t="shared" si="9"/>
-        <v>Chandelure 2</v>
-      </c>
-      <c r="F28">
-        <f>IF(AND(A28&lt;&gt;"",ISNUMBER(C28),D28&lt;&gt;""),_xlfn.XLOOKUP(A28,'Table of IDs'!M:M,'Table of IDs'!L:L),"")</f>
-        <v>609</v>
-      </c>
-      <c r="G28" t="str">
-        <f t="shared" si="3"/>
-        <v>0261</v>
-      </c>
-      <c r="H28" t="str" cm="1">
-        <f t="array" ref="H28">IF(G28&lt;&gt;"",RIGHT(G28,2)&amp;LEFT(G28,2)&amp;_xlfn.XLOOKUP(D28,'Table of IDs'!$C:C,'Table of IDs'!D:D)&amp;DEC2HEX(C28,2)&amp;DEC2HEX(B28,2),"")</f>
-        <v>6102610302FF</v>
-      </c>
-      <c r="I28" t="str">
-        <f t="shared" si="4"/>
-        <v>610202</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9">
-      <c r="A29" t="s">
-        <v>896</v>
-      </c>
-      <c r="B29">
-        <v>0</v>
-      </c>
-      <c r="C29">
-        <v>2</v>
-      </c>
-      <c r="D29" t="s">
-        <v>2272</v>
-      </c>
-      <c r="E29" t="str">
-        <f t="shared" si="9"/>
-        <v>Golurk 2</v>
-      </c>
-      <c r="F29">
-        <f>IF(AND(A29&lt;&gt;"",ISNUMBER(C29),D29&lt;&gt;""),_xlfn.XLOOKUP(A29,'Table of IDs'!M:M,'Table of IDs'!L:L),"")</f>
-        <v>623</v>
-      </c>
-      <c r="G29" t="str">
-        <f t="shared" si="3"/>
-        <v>026F</v>
-      </c>
-      <c r="H29" t="str" cm="1">
-        <f t="array" ref="H29">IF(G29&lt;&gt;"",RIGHT(G29,2)&amp;LEFT(G29,2)&amp;_xlfn.XLOOKUP(D29,'Table of IDs'!$C:C,'Table of IDs'!D:D)&amp;DEC2HEX(C29,2)&amp;DEC2HEX(B29,2),"")</f>
-        <v>6F0248030200</v>
-      </c>
-      <c r="I29" t="str">
-        <f t="shared" si="4"/>
-        <v>6F0202</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9">
-      <c r="A30" t="s">
-        <v>896</v>
-      </c>
-      <c r="B30">
-        <v>0</v>
-      </c>
-      <c r="C30">
-        <v>2</v>
-      </c>
-      <c r="D30" t="s">
-        <v>258</v>
-      </c>
-      <c r="E30" t="str">
-        <f t="shared" si="9"/>
-        <v>Golurk 2</v>
-      </c>
       <c r="F30">
         <f>IF(AND(A30&lt;&gt;"",ISNUMBER(C30),D30&lt;&gt;""),_xlfn.XLOOKUP(A30,'Table of IDs'!M:M,'Table of IDs'!L:L),"")</f>
-        <v>623</v>
+        <v>474</v>
       </c>
       <c r="G30" t="str">
-        <f t="shared" si="3"/>
-        <v>026F</v>
+        <f t="shared" si="9"/>
+        <v>01DA</v>
       </c>
       <c r="H30" t="str" cm="1">
         <f t="array" ref="H30">IF(G30&lt;&gt;"",RIGHT(G30,2)&amp;LEFT(G30,2)&amp;_xlfn.XLOOKUP(D30,'Table of IDs'!$C:C,'Table of IDs'!D:D)&amp;DEC2HEX(C30,2)&amp;DEC2HEX(B30,2),"")</f>
-        <v>6F0215030200</v>
+        <v>DA01160302FF</v>
       </c>
       <c r="I30" t="str">
-        <f t="shared" si="4"/>
-        <v/>
+        <f t="shared" si="10"/>
+        <v>DA0102</v>
       </c>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" t="s">
-        <v>896</v>
+        <v>773</v>
       </c>
       <c r="B31">
-        <v>1</v>
+        <v>255</v>
       </c>
       <c r="C31">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D31" t="s">
-        <v>2272</v>
+        <v>2305</v>
       </c>
       <c r="E31" t="str">
-        <f t="shared" si="9"/>
-        <v>Golurk 3</v>
+        <f t="shared" si="8"/>
+        <v>Emboar 2</v>
       </c>
       <c r="F31">
         <f>IF(AND(A31&lt;&gt;"",ISNUMBER(C31),D31&lt;&gt;""),_xlfn.XLOOKUP(A31,'Table of IDs'!M:M,'Table of IDs'!L:L),"")</f>
-        <v>623</v>
+        <v>500</v>
       </c>
       <c r="G31" t="str">
-        <f t="shared" si="3"/>
-        <v>026F</v>
+        <f t="shared" si="9"/>
+        <v>01F4</v>
       </c>
       <c r="H31" t="str" cm="1">
         <f t="array" ref="H31">IF(G31&lt;&gt;"",RIGHT(G31,2)&amp;LEFT(G31,2)&amp;_xlfn.XLOOKUP(D31,'Table of IDs'!$C:C,'Table of IDs'!D:D)&amp;DEC2HEX(C31,2)&amp;DEC2HEX(B31,2),"")</f>
-        <v>6F0248030301</v>
+        <v>F401780302FF</v>
       </c>
       <c r="I31" t="str">
-        <f t="shared" si="4"/>
-        <v>6F0203</v>
+        <f t="shared" si="10"/>
+        <v>F40102</v>
       </c>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" t="s">
-        <v>896</v>
+        <v>818</v>
       </c>
       <c r="B32">
-        <v>1</v>
+        <v>255</v>
       </c>
       <c r="C32">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D32" t="s">
-        <v>262</v>
+        <v>2318</v>
       </c>
       <c r="E32" t="str">
-        <f t="shared" si="9"/>
-        <v>Golurk 3</v>
+        <f t="shared" si="8"/>
+        <v>Scolipede 2</v>
       </c>
       <c r="F32">
         <f>IF(AND(A32&lt;&gt;"",ISNUMBER(C32),D32&lt;&gt;""),_xlfn.XLOOKUP(A32,'Table of IDs'!M:M,'Table of IDs'!L:L),"")</f>
-        <v>623</v>
+        <v>545</v>
       </c>
       <c r="G32" t="str">
-        <f t="shared" si="3"/>
-        <v>026F</v>
+        <f t="shared" si="9"/>
+        <v>0221</v>
       </c>
       <c r="H32" t="str" cm="1">
         <f t="array" ref="H32">IF(G32&lt;&gt;"",RIGHT(G32,2)&amp;LEFT(G32,2)&amp;_xlfn.XLOOKUP(D32,'Table of IDs'!$C:C,'Table of IDs'!D:D)&amp;DEC2HEX(C32,2)&amp;DEC2HEX(B32,2),"")</f>
-        <v>6F0219030301</v>
+        <v>2102830302FF</v>
       </c>
       <c r="I32" t="str">
-        <f t="shared" si="4"/>
-        <v/>
+        <f t="shared" si="10"/>
+        <v>210202</v>
       </c>
     </row>
     <row r="33" spans="1:9">
       <c r="A33" t="s">
-        <v>148</v>
+        <v>882</v>
       </c>
       <c r="B33">
-        <v>1</v>
+        <v>255</v>
       </c>
       <c r="C33">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D33" t="s">
-        <v>1712</v>
+        <v>2287</v>
       </c>
       <c r="E33" t="str">
-        <f t="shared" si="9"/>
-        <v>Kyurem 3</v>
+        <f t="shared" si="8"/>
+        <v>Chandelure 2</v>
       </c>
       <c r="F33">
         <f>IF(AND(A33&lt;&gt;"",ISNUMBER(C33),D33&lt;&gt;""),_xlfn.XLOOKUP(A33,'Table of IDs'!M:M,'Table of IDs'!L:L),"")</f>
-        <v>646</v>
+        <v>609</v>
       </c>
       <c r="G33" t="str">
-        <f t="shared" si="3"/>
-        <v>0286</v>
+        <f t="shared" si="9"/>
+        <v>0261</v>
       </c>
       <c r="H33" t="str" cm="1">
         <f t="array" ref="H33">IF(G33&lt;&gt;"",RIGHT(G33,2)&amp;LEFT(G33,2)&amp;_xlfn.XLOOKUP(D33,'Table of IDs'!$C:C,'Table of IDs'!D:D)&amp;DEC2HEX(C33,2)&amp;DEC2HEX(B33,2),"")</f>
-        <v>860220020301</v>
+        <v>6102610302FF</v>
       </c>
       <c r="I33" t="str">
-        <f t="shared" si="4"/>
-        <v>860203</v>
+        <f t="shared" si="10"/>
+        <v>610202</v>
       </c>
     </row>
     <row r="34" spans="1:9">
       <c r="A34" t="s">
-        <v>148</v>
+        <v>896</v>
       </c>
       <c r="B34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C34">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D34" t="s">
-        <v>1579</v>
+        <v>2271</v>
       </c>
       <c r="E34" t="str">
-        <f t="shared" si="9"/>
-        <v>Kyurem 3</v>
+        <f t="shared" si="8"/>
+        <v>Golurk 2</v>
       </c>
       <c r="F34">
         <f>IF(AND(A34&lt;&gt;"",ISNUMBER(C34),D34&lt;&gt;""),_xlfn.XLOOKUP(A34,'Table of IDs'!M:M,'Table of IDs'!L:L),"")</f>
-        <v>646</v>
+        <v>623</v>
       </c>
       <c r="G34" t="str">
-        <f t="shared" si="3"/>
-        <v>0286</v>
+        <f t="shared" si="9"/>
+        <v>026F</v>
       </c>
       <c r="H34" t="str" cm="1">
         <f t="array" ref="H34">IF(G34&lt;&gt;"",RIGHT(G34,2)&amp;LEFT(G34,2)&amp;_xlfn.XLOOKUP(D34,'Table of IDs'!$C:C,'Table of IDs'!D:D)&amp;DEC2HEX(C34,2)&amp;DEC2HEX(B34,2),"")</f>
-        <v>860237010301</v>
+        <v>6F0248030200</v>
       </c>
       <c r="I34" t="str">
-        <f t="shared" si="4"/>
-        <v/>
+        <f t="shared" si="10"/>
+        <v>6F0202</v>
       </c>
     </row>
     <row r="35" spans="1:9">
       <c r="A35" t="s">
-        <v>148</v>
+        <v>896</v>
       </c>
       <c r="B35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C35">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D35" t="s">
-        <v>1570</v>
+        <v>258</v>
       </c>
       <c r="E35" t="str">
-        <f t="shared" si="9"/>
-        <v>Kyurem 3</v>
+        <f t="shared" si="8"/>
+        <v>Golurk 2</v>
       </c>
       <c r="F35">
         <f>IF(AND(A35&lt;&gt;"",ISNUMBER(C35),D35&lt;&gt;""),_xlfn.XLOOKUP(A35,'Table of IDs'!M:M,'Table of IDs'!L:L),"")</f>
-        <v>646</v>
+        <v>623</v>
       </c>
       <c r="G35" t="str">
-        <f t="shared" si="3"/>
-        <v>0286</v>
+        <f t="shared" si="9"/>
+        <v>026F</v>
       </c>
       <c r="H35" t="str" cm="1">
         <f t="array" ref="H35">IF(G35&lt;&gt;"",RIGHT(G35,2)&amp;LEFT(G35,2)&amp;_xlfn.XLOOKUP(D35,'Table of IDs'!$C:C,'Table of IDs'!D:D)&amp;DEC2HEX(C35,2)&amp;DEC2HEX(B35,2),"")</f>
-        <v>86022E010301</v>
+        <v>6F0215030200</v>
       </c>
       <c r="I35" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="36" spans="1:9">
       <c r="A36" t="s">
-        <v>148</v>
+        <v>896</v>
       </c>
       <c r="B36">
         <v>1</v>
@@ -8901,60 +8973,60 @@
         <v>3</v>
       </c>
       <c r="D36" t="s">
-        <v>266</v>
+        <v>2271</v>
       </c>
       <c r="E36" t="str">
-        <f t="shared" si="9"/>
-        <v>Kyurem 3</v>
+        <f t="shared" si="8"/>
+        <v>Golurk 3</v>
       </c>
       <c r="F36">
         <f>IF(AND(A36&lt;&gt;"",ISNUMBER(C36),D36&lt;&gt;""),_xlfn.XLOOKUP(A36,'Table of IDs'!M:M,'Table of IDs'!L:L),"")</f>
-        <v>646</v>
+        <v>623</v>
       </c>
       <c r="G36" t="str">
-        <f t="shared" si="3"/>
-        <v>0286</v>
+        <f t="shared" si="9"/>
+        <v>026F</v>
       </c>
       <c r="H36" t="str" cm="1">
         <f t="array" ref="H36">IF(G36&lt;&gt;"",RIGHT(G36,2)&amp;LEFT(G36,2)&amp;_xlfn.XLOOKUP(D36,'Table of IDs'!$C:C,'Table of IDs'!D:D)&amp;DEC2HEX(C36,2)&amp;DEC2HEX(B36,2),"")</f>
-        <v>86029B030301</v>
+        <v>6F0248030301</v>
       </c>
       <c r="I36" t="str">
-        <f t="shared" si="4"/>
-        <v/>
+        <f t="shared" si="10"/>
+        <v>6F0203</v>
       </c>
     </row>
     <row r="37" spans="1:9">
       <c r="A37" t="s">
-        <v>148</v>
+        <v>896</v>
       </c>
       <c r="B37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C37">
         <v>3</v>
       </c>
       <c r="D37" t="s">
-        <v>1712</v>
+        <v>262</v>
       </c>
       <c r="E37" t="str">
-        <f t="shared" si="9"/>
-        <v>Kyurem 3</v>
+        <f t="shared" si="8"/>
+        <v>Golurk 3</v>
       </c>
       <c r="F37">
         <f>IF(AND(A37&lt;&gt;"",ISNUMBER(C37),D37&lt;&gt;""),_xlfn.XLOOKUP(A37,'Table of IDs'!M:M,'Table of IDs'!L:L),"")</f>
-        <v>646</v>
+        <v>623</v>
       </c>
       <c r="G37" t="str">
-        <f t="shared" si="3"/>
-        <v>0286</v>
+        <f t="shared" si="9"/>
+        <v>026F</v>
       </c>
       <c r="H37" t="str" cm="1">
         <f t="array" ref="H37">IF(G37&lt;&gt;"",RIGHT(G37,2)&amp;LEFT(G37,2)&amp;_xlfn.XLOOKUP(D37,'Table of IDs'!$C:C,'Table of IDs'!D:D)&amp;DEC2HEX(C37,2)&amp;DEC2HEX(B37,2),"")</f>
-        <v>860220020302</v>
+        <v>6F0219030301</v>
       </c>
       <c r="I37" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -8963,16 +9035,16 @@
         <v>148</v>
       </c>
       <c r="B38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C38">
         <v>3</v>
       </c>
       <c r="D38" t="s">
-        <v>1579</v>
+        <v>1712</v>
       </c>
       <c r="E38" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>Kyurem 3</v>
       </c>
       <c r="F38">
@@ -8980,16 +9052,16 @@
         <v>646</v>
       </c>
       <c r="G38" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v>0286</v>
       </c>
       <c r="H38" t="str" cm="1">
         <f t="array" ref="H38">IF(G38&lt;&gt;"",RIGHT(G38,2)&amp;LEFT(G38,2)&amp;_xlfn.XLOOKUP(D38,'Table of IDs'!$C:C,'Table of IDs'!D:D)&amp;DEC2HEX(C38,2)&amp;DEC2HEX(B38,2),"")</f>
-        <v>860237010302</v>
+        <v>860220020301</v>
       </c>
       <c r="I38" t="str">
-        <f t="shared" si="4"/>
-        <v/>
+        <f t="shared" si="10"/>
+        <v>860203</v>
       </c>
     </row>
     <row r="39" spans="1:9">
@@ -8997,16 +9069,16 @@
         <v>148</v>
       </c>
       <c r="B39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C39">
         <v>3</v>
       </c>
       <c r="D39" t="s">
-        <v>1570</v>
+        <v>1579</v>
       </c>
       <c r="E39" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>Kyurem 3</v>
       </c>
       <c r="F39">
@@ -9014,15 +9086,15 @@
         <v>646</v>
       </c>
       <c r="G39" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v>0286</v>
       </c>
       <c r="H39" t="str" cm="1">
         <f t="array" ref="H39">IF(G39&lt;&gt;"",RIGHT(G39,2)&amp;LEFT(G39,2)&amp;_xlfn.XLOOKUP(D39,'Table of IDs'!$C:C,'Table of IDs'!D:D)&amp;DEC2HEX(C39,2)&amp;DEC2HEX(B39,2),"")</f>
-        <v>86022E010302</v>
+        <v>860237010301</v>
       </c>
       <c r="I39" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -9031,16 +9103,16 @@
         <v>148</v>
       </c>
       <c r="B40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C40">
         <v>3</v>
       </c>
       <c r="D40" t="s">
-        <v>266</v>
+        <v>1570</v>
       </c>
       <c r="E40" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>Kyurem 3</v>
       </c>
       <c r="F40">
@@ -9048,370 +9120,642 @@
         <v>646</v>
       </c>
       <c r="G40" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v>0286</v>
       </c>
       <c r="H40" t="str" cm="1">
         <f t="array" ref="H40">IF(G40&lt;&gt;"",RIGHT(G40,2)&amp;LEFT(G40,2)&amp;_xlfn.XLOOKUP(D40,'Table of IDs'!$C:C,'Table of IDs'!D:D)&amp;DEC2HEX(C40,2)&amp;DEC2HEX(B40,2),"")</f>
-        <v>86029B030302</v>
+        <v>86022E010301</v>
       </c>
       <c r="I40" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="41" spans="1:9">
       <c r="A41" t="s">
-        <v>930</v>
+        <v>148</v>
       </c>
       <c r="B41">
-        <v>255</v>
+        <v>1</v>
       </c>
       <c r="C41">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D41" t="s">
-        <v>241</v>
+        <v>266</v>
       </c>
       <c r="E41" t="str">
-        <f t="shared" si="9"/>
-        <v>Greninja 1</v>
+        <f t="shared" ref="E41:E60" si="11">_xlfn.CONCAT(A41," ",C41)</f>
+        <v>Kyurem 3</v>
       </c>
       <c r="F41">
         <f>IF(AND(A41&lt;&gt;"",ISNUMBER(C41),D41&lt;&gt;""),_xlfn.XLOOKUP(A41,'Table of IDs'!M:M,'Table of IDs'!L:L),"")</f>
-        <v>658</v>
+        <v>646</v>
       </c>
       <c r="G41" t="str">
-        <f t="shared" si="3"/>
-        <v>0292</v>
+        <f t="shared" ref="G41:G60" si="12">IF(F41&lt;&gt;"",DEC2HEX(F41,4),"")</f>
+        <v>0286</v>
       </c>
       <c r="H41" t="str" cm="1">
         <f t="array" ref="H41">IF(G41&lt;&gt;"",RIGHT(G41,2)&amp;LEFT(G41,2)&amp;_xlfn.XLOOKUP(D41,'Table of IDs'!$C:C,'Table of IDs'!D:D)&amp;DEC2HEX(C41,2)&amp;DEC2HEX(B41,2),"")</f>
-        <v>92020A0301FF</v>
+        <v>86029B030301</v>
       </c>
       <c r="I41" t="str">
-        <f t="shared" si="4"/>
-        <v>920201</v>
+        <f t="shared" ref="I41:I60" si="13">IF(OR(A41&lt;&gt;A40,C41&lt;&gt;C40),LEFT(H41,4)&amp;LEFT(RIGHT(H41,4),2),"")</f>
+        <v/>
       </c>
     </row>
     <row r="42" spans="1:9">
       <c r="A42" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B42">
-        <v>255</v>
+        <v>2</v>
       </c>
       <c r="C42">
         <v>3</v>
       </c>
       <c r="D42" t="s">
-        <v>260</v>
+        <v>1712</v>
       </c>
       <c r="E42" t="str">
-        <f t="shared" si="9"/>
-        <v>Yveltal 3</v>
+        <f t="shared" si="11"/>
+        <v>Kyurem 3</v>
       </c>
       <c r="F42">
         <f>IF(AND(A42&lt;&gt;"",ISNUMBER(C42),D42&lt;&gt;""),_xlfn.XLOOKUP(A42,'Table of IDs'!M:M,'Table of IDs'!L:L),"")</f>
-        <v>717</v>
+        <v>646</v>
       </c>
       <c r="G42" t="str">
-        <f t="shared" si="3"/>
-        <v>02CD</v>
+        <f t="shared" si="12"/>
+        <v>0286</v>
       </c>
       <c r="H42" t="str" cm="1">
         <f t="array" ref="H42">IF(G42&lt;&gt;"",RIGHT(G42,2)&amp;LEFT(G42,2)&amp;_xlfn.XLOOKUP(D42,'Table of IDs'!$C:C,'Table of IDs'!D:D)&amp;DEC2HEX(C42,2)&amp;DEC2HEX(B42,2),"")</f>
-        <v>CD02170303FF</v>
+        <v>860220020302</v>
       </c>
       <c r="I42" t="str">
-        <f t="shared" si="4"/>
-        <v>CD0203</v>
+        <f t="shared" si="13"/>
+        <v/>
       </c>
     </row>
     <row r="43" spans="1:9">
       <c r="A43" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B43">
-        <v>255</v>
+        <v>2</v>
       </c>
       <c r="C43">
         <v>3</v>
       </c>
       <c r="D43" t="s">
-        <v>266</v>
+        <v>1579</v>
       </c>
       <c r="E43" t="str">
-        <f t="shared" si="9"/>
-        <v>Yveltal 3</v>
+        <f t="shared" si="11"/>
+        <v>Kyurem 3</v>
       </c>
       <c r="F43">
         <f>IF(AND(A43&lt;&gt;"",ISNUMBER(C43),D43&lt;&gt;""),_xlfn.XLOOKUP(A43,'Table of IDs'!M:M,'Table of IDs'!L:L),"")</f>
-        <v>717</v>
+        <v>646</v>
       </c>
       <c r="G43" t="str">
-        <f t="shared" si="3"/>
-        <v>02CD</v>
+        <f t="shared" si="12"/>
+        <v>0286</v>
       </c>
       <c r="H43" t="str" cm="1">
         <f t="array" ref="H43">IF(G43&lt;&gt;"",RIGHT(G43,2)&amp;LEFT(G43,2)&amp;_xlfn.XLOOKUP(D43,'Table of IDs'!$C:C,'Table of IDs'!D:D)&amp;DEC2HEX(C43,2)&amp;DEC2HEX(B43,2),"")</f>
-        <v>CD029B0303FF</v>
+        <v>860237010302</v>
       </c>
       <c r="I43" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
     <row r="44" spans="1:9">
       <c r="A44" t="s">
-        <v>1048</v>
+        <v>148</v>
       </c>
       <c r="B44">
-        <v>255</v>
+        <v>2</v>
       </c>
       <c r="C44">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D44" t="s">
-        <v>261</v>
+        <v>1570</v>
       </c>
       <c r="E44" t="str">
-        <f t="shared" si="9"/>
-        <v>Togedemaru 1</v>
+        <f t="shared" si="11"/>
+        <v>Kyurem 3</v>
       </c>
       <c r="F44">
         <f>IF(AND(A44&lt;&gt;"",ISNUMBER(C44),D44&lt;&gt;""),_xlfn.XLOOKUP(A44,'Table of IDs'!M:M,'Table of IDs'!L:L),"")</f>
-        <v>777</v>
+        <v>646</v>
       </c>
       <c r="G44" t="str">
-        <f t="shared" si="3"/>
-        <v>0309</v>
+        <f t="shared" si="12"/>
+        <v>0286</v>
       </c>
       <c r="H44" t="str" cm="1">
         <f t="array" ref="H44">IF(G44&lt;&gt;"",RIGHT(G44,2)&amp;LEFT(G44,2)&amp;_xlfn.XLOOKUP(D44,'Table of IDs'!$C:C,'Table of IDs'!D:D)&amp;DEC2HEX(C44,2)&amp;DEC2HEX(B44,2),"")</f>
-        <v>0903180301FF</v>
+        <v>86022E010302</v>
       </c>
       <c r="I44" t="str">
-        <f t="shared" si="4"/>
-        <v>090301</v>
+        <f t="shared" si="13"/>
+        <v/>
       </c>
     </row>
     <row r="45" spans="1:9">
       <c r="A45" t="s">
-        <v>1055</v>
+        <v>148</v>
       </c>
       <c r="B45">
-        <v>255</v>
+        <v>2</v>
       </c>
       <c r="C45">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D45" t="s">
-        <v>1085</v>
+        <v>266</v>
       </c>
       <c r="E45" t="str">
-        <f t="shared" si="9"/>
-        <v>Kommo-o 1</v>
+        <f t="shared" si="11"/>
+        <v>Kyurem 3</v>
       </c>
       <c r="F45">
         <f>IF(AND(A45&lt;&gt;"",ISNUMBER(C45),D45&lt;&gt;""),_xlfn.XLOOKUP(A45,'Table of IDs'!M:M,'Table of IDs'!L:L),"")</f>
-        <v>784</v>
+        <v>646</v>
       </c>
       <c r="G45" t="str">
-        <f t="shared" si="3"/>
-        <v>0310</v>
+        <f t="shared" si="12"/>
+        <v>0286</v>
       </c>
       <c r="H45" t="str" cm="1">
         <f t="array" ref="H45">IF(G45&lt;&gt;"",RIGHT(G45,2)&amp;LEFT(G45,2)&amp;_xlfn.XLOOKUP(D45,'Table of IDs'!$C:C,'Table of IDs'!D:D)&amp;DEC2HEX(C45,2)&amp;DEC2HEX(B45,2),"")</f>
-        <v>10039E0301FF</v>
+        <v>86029B030302</v>
       </c>
       <c r="I45" t="str">
-        <f t="shared" si="4"/>
-        <v>100301</v>
+        <f t="shared" si="13"/>
+        <v/>
       </c>
     </row>
     <row r="46" spans="1:9">
       <c r="A46" t="s">
-        <v>144</v>
+        <v>930</v>
       </c>
       <c r="B46">
+        <v>255</v>
+      </c>
+      <c r="C46">
         <v>1</v>
       </c>
-      <c r="C46">
-        <v>3</v>
-      </c>
       <c r="D46" t="s">
-        <v>266</v>
+        <v>241</v>
       </c>
       <c r="E46" t="str">
-        <f t="shared" si="9"/>
-        <v>Necrozma 3</v>
+        <f t="shared" si="11"/>
+        <v>Greninja 1</v>
       </c>
       <c r="F46">
         <f>IF(AND(A46&lt;&gt;"",ISNUMBER(C46),D46&lt;&gt;""),_xlfn.XLOOKUP(A46,'Table of IDs'!M:M,'Table of IDs'!L:L),"")</f>
-        <v>800</v>
+        <v>658</v>
       </c>
       <c r="G46" t="str">
-        <f t="shared" si="3"/>
-        <v>0320</v>
+        <f t="shared" si="12"/>
+        <v>0292</v>
       </c>
       <c r="H46" t="str" cm="1">
         <f t="array" ref="H46">IF(G46&lt;&gt;"",RIGHT(G46,2)&amp;LEFT(G46,2)&amp;_xlfn.XLOOKUP(D46,'Table of IDs'!$C:C,'Table of IDs'!D:D)&amp;DEC2HEX(C46,2)&amp;DEC2HEX(B46,2),"")</f>
-        <v>20039B030301</v>
+        <v>92020A0301FF</v>
       </c>
       <c r="I46" t="str">
-        <f t="shared" si="4"/>
-        <v>200303</v>
+        <f t="shared" si="13"/>
+        <v>920201</v>
       </c>
     </row>
     <row r="47" spans="1:9">
       <c r="A47" t="s">
-        <v>144</v>
+        <v>940</v>
       </c>
       <c r="B47">
+        <v>255</v>
+      </c>
+      <c r="C47">
         <v>2</v>
       </c>
-      <c r="C47">
-        <v>3</v>
-      </c>
       <c r="D47" t="s">
-        <v>266</v>
+        <v>2317</v>
       </c>
       <c r="E47" t="str">
-        <f t="shared" ref="E47" si="10">_xlfn.CONCAT(A47," ",C47)</f>
-        <v>Necrozma 3</v>
+        <f t="shared" si="11"/>
+        <v>Pyroar 2</v>
       </c>
       <c r="F47">
         <f>IF(AND(A47&lt;&gt;"",ISNUMBER(C47),D47&lt;&gt;""),_xlfn.XLOOKUP(A47,'Table of IDs'!M:M,'Table of IDs'!L:L),"")</f>
-        <v>800</v>
+        <v>668</v>
       </c>
       <c r="G47" t="str">
-        <f t="shared" ref="G47" si="11">IF(F47&lt;&gt;"",DEC2HEX(F47,4),"")</f>
-        <v>0320</v>
+        <f t="shared" si="12"/>
+        <v>029C</v>
       </c>
       <c r="H47" t="str" cm="1">
         <f t="array" ref="H47">IF(G47&lt;&gt;"",RIGHT(G47,2)&amp;LEFT(G47,2)&amp;_xlfn.XLOOKUP(D47,'Table of IDs'!$C:C,'Table of IDs'!D:D)&amp;DEC2HEX(C47,2)&amp;DEC2HEX(B47,2),"")</f>
-        <v>20039B030302</v>
+        <v>9C02820302FF</v>
       </c>
       <c r="I47" t="str">
-        <f t="shared" ref="I47" si="12">IF(OR(A47&lt;&gt;A46,C47&lt;&gt;C46),LEFT(H47,4)&amp;LEFT(RIGHT(H47,4),2),"")</f>
-        <v/>
+        <f t="shared" si="13"/>
+        <v>9C0202</v>
       </c>
     </row>
     <row r="48" spans="1:9">
+      <c r="A48" t="s">
+        <v>950</v>
+      </c>
+      <c r="B48">
+        <v>255</v>
+      </c>
+      <c r="C48">
+        <v>2</v>
+      </c>
+      <c r="D48" t="s">
+        <v>2307</v>
+      </c>
       <c r="E48" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="F48" t="str">
+        <f t="shared" si="11"/>
+        <v>Meowstic 2</v>
+      </c>
+      <c r="F48">
         <f>IF(AND(A48&lt;&gt;"",ISNUMBER(C48),D48&lt;&gt;""),_xlfn.XLOOKUP(A48,'Table of IDs'!M:M,'Table of IDs'!L:L),"")</f>
-        <v/>
+        <v>678</v>
       </c>
       <c r="G48" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+        <f t="shared" si="12"/>
+        <v>02A6</v>
       </c>
       <c r="H48" t="str" cm="1">
         <f t="array" ref="H48">IF(G48&lt;&gt;"",RIGHT(G48,2)&amp;LEFT(G48,2)&amp;_xlfn.XLOOKUP(D48,'Table of IDs'!$C:C,'Table of IDs'!D:D)&amp;DEC2HEX(C48,2)&amp;DEC2HEX(B48,2),"")</f>
-        <v/>
+        <v>A6027A0302FF</v>
       </c>
       <c r="I48" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="49" spans="5:9">
+        <f t="shared" si="13"/>
+        <v>A60202</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9">
+      <c r="A49" t="s">
+        <v>959</v>
+      </c>
+      <c r="B49">
+        <v>255</v>
+      </c>
+      <c r="C49">
+        <v>2</v>
+      </c>
+      <c r="D49" t="s">
+        <v>2316</v>
+      </c>
       <c r="E49" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="F49" t="str">
+        <f t="shared" si="11"/>
+        <v>Malamar 2</v>
+      </c>
+      <c r="F49">
         <f>IF(AND(A49&lt;&gt;"",ISNUMBER(C49),D49&lt;&gt;""),_xlfn.XLOOKUP(A49,'Table of IDs'!M:M,'Table of IDs'!L:L),"")</f>
-        <v/>
+        <v>687</v>
       </c>
       <c r="G49" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+        <f t="shared" si="12"/>
+        <v>02AF</v>
       </c>
       <c r="H49" t="str" cm="1">
         <f t="array" ref="H49">IF(G49&lt;&gt;"",RIGHT(G49,2)&amp;LEFT(G49,2)&amp;_xlfn.XLOOKUP(D49,'Table of IDs'!$C:C,'Table of IDs'!D:D)&amp;DEC2HEX(C49,2)&amp;DEC2HEX(B49,2),"")</f>
-        <v/>
+        <v>AF02810302FF</v>
       </c>
       <c r="I49" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="50" spans="5:9">
+        <f t="shared" si="13"/>
+        <v>AF0202</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9">
+      <c r="A50" t="s">
+        <v>145</v>
+      </c>
+      <c r="B50">
+        <v>255</v>
+      </c>
+      <c r="C50">
+        <v>3</v>
+      </c>
+      <c r="D50" t="s">
+        <v>260</v>
+      </c>
       <c r="E50" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="F50" t="str">
+        <f t="shared" si="11"/>
+        <v>Yveltal 3</v>
+      </c>
+      <c r="F50">
         <f>IF(AND(A50&lt;&gt;"",ISNUMBER(C50),D50&lt;&gt;""),_xlfn.XLOOKUP(A50,'Table of IDs'!M:M,'Table of IDs'!L:L),"")</f>
-        <v/>
+        <v>717</v>
       </c>
       <c r="G50" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+        <f t="shared" si="12"/>
+        <v>02CD</v>
       </c>
       <c r="H50" t="str" cm="1">
         <f t="array" ref="H50">IF(G50&lt;&gt;"",RIGHT(G50,2)&amp;LEFT(G50,2)&amp;_xlfn.XLOOKUP(D50,'Table of IDs'!$C:C,'Table of IDs'!D:D)&amp;DEC2HEX(C50,2)&amp;DEC2HEX(B50,2),"")</f>
-        <v/>
+        <v>CD02170303FF</v>
       </c>
       <c r="I50" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="51" spans="5:9">
+        <f t="shared" si="13"/>
+        <v>CD0203</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9">
+      <c r="A51" t="s">
+        <v>145</v>
+      </c>
+      <c r="B51">
+        <v>255</v>
+      </c>
+      <c r="C51">
+        <v>3</v>
+      </c>
+      <c r="D51" t="s">
+        <v>266</v>
+      </c>
       <c r="E51" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="F51" t="str">
+        <f t="shared" si="11"/>
+        <v>Yveltal 3</v>
+      </c>
+      <c r="F51">
         <f>IF(AND(A51&lt;&gt;"",ISNUMBER(C51),D51&lt;&gt;""),_xlfn.XLOOKUP(A51,'Table of IDs'!M:M,'Table of IDs'!L:L),"")</f>
-        <v/>
+        <v>717</v>
       </c>
       <c r="G51" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+        <f t="shared" si="12"/>
+        <v>02CD</v>
       </c>
       <c r="H51" t="str" cm="1">
         <f t="array" ref="H51">IF(G51&lt;&gt;"",RIGHT(G51,2)&amp;LEFT(G51,2)&amp;_xlfn.XLOOKUP(D51,'Table of IDs'!$C:C,'Table of IDs'!D:D)&amp;DEC2HEX(C51,2)&amp;DEC2HEX(B51,2),"")</f>
+        <v>CD029B0303FF</v>
+      </c>
+      <c r="I51" t="str">
+        <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="I51" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="52" spans="5:9">
+    </row>
+    <row r="52" spans="1:9">
+      <c r="A52" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B52">
+        <v>255</v>
+      </c>
+      <c r="C52">
+        <v>1</v>
+      </c>
+      <c r="D52" t="s">
+        <v>261</v>
+      </c>
       <c r="E52" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="F52" t="str">
+        <f t="shared" si="11"/>
+        <v>Togedemaru 1</v>
+      </c>
+      <c r="F52">
         <f>IF(AND(A52&lt;&gt;"",ISNUMBER(C52),D52&lt;&gt;""),_xlfn.XLOOKUP(A52,'Table of IDs'!M:M,'Table of IDs'!L:L),"")</f>
-        <v/>
+        <v>777</v>
       </c>
       <c r="G52" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+        <f t="shared" si="12"/>
+        <v>0309</v>
       </c>
       <c r="H52" t="str" cm="1">
         <f t="array" ref="H52">IF(G52&lt;&gt;"",RIGHT(G52,2)&amp;LEFT(G52,2)&amp;_xlfn.XLOOKUP(D52,'Table of IDs'!$C:C,'Table of IDs'!D:D)&amp;DEC2HEX(C52,2)&amp;DEC2HEX(B52,2),"")</f>
+        <v>0903180301FF</v>
+      </c>
+      <c r="I52" t="str">
+        <f t="shared" si="13"/>
+        <v>090301</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9">
+      <c r="A53" t="s">
+        <v>1055</v>
+      </c>
+      <c r="B53">
+        <v>255</v>
+      </c>
+      <c r="C53">
+        <v>1</v>
+      </c>
+      <c r="D53" t="s">
+        <v>1085</v>
+      </c>
+      <c r="E53" t="str">
+        <f t="shared" si="11"/>
+        <v>Kommo-o 1</v>
+      </c>
+      <c r="F53">
+        <f>IF(AND(A53&lt;&gt;"",ISNUMBER(C53),D53&lt;&gt;""),_xlfn.XLOOKUP(A53,'Table of IDs'!M:M,'Table of IDs'!L:L),"")</f>
+        <v>784</v>
+      </c>
+      <c r="G53" t="str">
+        <f t="shared" si="12"/>
+        <v>0310</v>
+      </c>
+      <c r="H53" t="str" cm="1">
+        <f t="array" ref="H53">IF(G53&lt;&gt;"",RIGHT(G53,2)&amp;LEFT(G53,2)&amp;_xlfn.XLOOKUP(D53,'Table of IDs'!$C:C,'Table of IDs'!D:D)&amp;DEC2HEX(C53,2)&amp;DEC2HEX(B53,2),"")</f>
+        <v>10039E0301FF</v>
+      </c>
+      <c r="I53" t="str">
+        <f t="shared" si="13"/>
+        <v>100301</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9">
+      <c r="A54" t="s">
+        <v>144</v>
+      </c>
+      <c r="B54">
+        <v>1</v>
+      </c>
+      <c r="C54">
+        <v>3</v>
+      </c>
+      <c r="D54" t="s">
+        <v>266</v>
+      </c>
+      <c r="E54" t="str">
+        <f t="shared" si="11"/>
+        <v>Necrozma 3</v>
+      </c>
+      <c r="F54">
+        <f>IF(AND(A54&lt;&gt;"",ISNUMBER(C54),D54&lt;&gt;""),_xlfn.XLOOKUP(A54,'Table of IDs'!M:M,'Table of IDs'!L:L),"")</f>
+        <v>800</v>
+      </c>
+      <c r="G54" t="str">
+        <f t="shared" si="12"/>
+        <v>0320</v>
+      </c>
+      <c r="H54" t="str" cm="1">
+        <f t="array" ref="H54">IF(G54&lt;&gt;"",RIGHT(G54,2)&amp;LEFT(G54,2)&amp;_xlfn.XLOOKUP(D54,'Table of IDs'!$C:C,'Table of IDs'!D:D)&amp;DEC2HEX(C54,2)&amp;DEC2HEX(B54,2),"")</f>
+        <v>20039B030301</v>
+      </c>
+      <c r="I54" t="str">
+        <f t="shared" si="13"/>
+        <v>200303</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9">
+      <c r="A55" t="s">
+        <v>144</v>
+      </c>
+      <c r="B55">
+        <v>2</v>
+      </c>
+      <c r="C55">
+        <v>3</v>
+      </c>
+      <c r="D55" t="s">
+        <v>266</v>
+      </c>
+      <c r="E55" t="str">
+        <f t="shared" si="11"/>
+        <v>Necrozma 3</v>
+      </c>
+      <c r="F55">
+        <f>IF(AND(A55&lt;&gt;"",ISNUMBER(C55),D55&lt;&gt;""),_xlfn.XLOOKUP(A55,'Table of IDs'!M:M,'Table of IDs'!L:L),"")</f>
+        <v>800</v>
+      </c>
+      <c r="G55" t="str">
+        <f t="shared" si="12"/>
+        <v>0320</v>
+      </c>
+      <c r="H55" t="str" cm="1">
+        <f t="array" ref="H55">IF(G55&lt;&gt;"",RIGHT(G55,2)&amp;LEFT(G55,2)&amp;_xlfn.XLOOKUP(D55,'Table of IDs'!$C:C,'Table of IDs'!D:D)&amp;DEC2HEX(C55,2)&amp;DEC2HEX(B55,2),"")</f>
+        <v>20039B030302</v>
+      </c>
+      <c r="I55" t="str">
+        <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="I52" t="str">
-        <f t="shared" si="4"/>
+    </row>
+    <row r="56" spans="1:9">
+      <c r="E56" t="str">
+        <f t="shared" si="11"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="F56" t="str">
+        <f>IF(AND(A56&lt;&gt;"",ISNUMBER(C56),D56&lt;&gt;""),_xlfn.XLOOKUP(A56,'Table of IDs'!M:M,'Table of IDs'!L:L),"")</f>
         <v/>
       </c>
+      <c r="G56" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="H56" t="str" cm="1">
+        <f t="array" ref="H56">IF(G56&lt;&gt;"",RIGHT(G56,2)&amp;LEFT(G56,2)&amp;_xlfn.XLOOKUP(D56,'Table of IDs'!$C:C,'Table of IDs'!D:D)&amp;DEC2HEX(C56,2)&amp;DEC2HEX(B56,2),"")</f>
+        <v/>
+      </c>
+      <c r="I56" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+    </row>
+    <row r="57" spans="1:9">
+      <c r="E57" t="str">
+        <f t="shared" si="11"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="F57" t="str">
+        <f>IF(AND(A57&lt;&gt;"",ISNUMBER(C57),D57&lt;&gt;""),_xlfn.XLOOKUP(A57,'Table of IDs'!M:M,'Table of IDs'!L:L),"")</f>
+        <v/>
+      </c>
+      <c r="G57" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="H57" t="str" cm="1">
+        <f t="array" ref="H57">IF(G57&lt;&gt;"",RIGHT(G57,2)&amp;LEFT(G57,2)&amp;_xlfn.XLOOKUP(D57,'Table of IDs'!$C:C,'Table of IDs'!D:D)&amp;DEC2HEX(C57,2)&amp;DEC2HEX(B57,2),"")</f>
+        <v/>
+      </c>
+      <c r="I57" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+    </row>
+    <row r="58" spans="1:9">
+      <c r="E58" t="str">
+        <f t="shared" si="11"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="F58" t="str">
+        <f>IF(AND(A58&lt;&gt;"",ISNUMBER(C58),D58&lt;&gt;""),_xlfn.XLOOKUP(A58,'Table of IDs'!M:M,'Table of IDs'!L:L),"")</f>
+        <v/>
+      </c>
+      <c r="G58" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="H58" t="str" cm="1">
+        <f t="array" ref="H58">IF(G58&lt;&gt;"",RIGHT(G58,2)&amp;LEFT(G58,2)&amp;_xlfn.XLOOKUP(D58,'Table of IDs'!$C:C,'Table of IDs'!D:D)&amp;DEC2HEX(C58,2)&amp;DEC2HEX(B58,2),"")</f>
+        <v/>
+      </c>
+      <c r="I58" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+    </row>
+    <row r="59" spans="1:9">
+      <c r="E59" t="str">
+        <f t="shared" si="11"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="F59" t="str">
+        <f>IF(AND(A59&lt;&gt;"",ISNUMBER(C59),D59&lt;&gt;""),_xlfn.XLOOKUP(A59,'Table of IDs'!M:M,'Table of IDs'!L:L),"")</f>
+        <v/>
+      </c>
+      <c r="G59" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="H59" t="str" cm="1">
+        <f t="array" ref="H59">IF(G59&lt;&gt;"",RIGHT(G59,2)&amp;LEFT(G59,2)&amp;_xlfn.XLOOKUP(D59,'Table of IDs'!$C:C,'Table of IDs'!D:D)&amp;DEC2HEX(C59,2)&amp;DEC2HEX(B59,2),"")</f>
+        <v/>
+      </c>
+      <c r="I59" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+    </row>
+    <row r="60" spans="1:9">
+      <c r="E60" t="str">
+        <f t="shared" si="11"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="F60" t="str">
+        <f>IF(AND(A60&lt;&gt;"",ISNUMBER(C60),D60&lt;&gt;""),_xlfn.XLOOKUP(A60,'Table of IDs'!M:M,'Table of IDs'!L:L),"")</f>
+        <v/>
+      </c>
+      <c r="G60" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="H60" t="str" cm="1">
+        <f t="array" ref="H60">IF(G60&lt;&gt;"",RIGHT(G60,2)&amp;LEFT(G60,2)&amp;_xlfn.XLOOKUP(D60,'Table of IDs'!$C:C,'Table of IDs'!D:D)&amp;DEC2HEX(C60,2)&amp;DEC2HEX(B60,2),"")</f>
+        <v/>
+      </c>
+      <c r="I60" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F53">
-    <sortCondition ref="F2:F53"/>
-    <sortCondition ref="D2:D53"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F61">
+    <sortCondition ref="F2:F61"/>
+    <sortCondition ref="D2:D61"/>
   </sortState>
   <dataValidations count="1">
     <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B1048576" xr:uid="{4B5C337F-D26E-4BD7-93B7-85D97DC31187}">
@@ -9443,7 +9787,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8FC3AD1-C92D-4EF3-990D-90FF3B9AFC91}">
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr defaultRowHeight="14.15"/>
   <cols>
     <col min="1" max="1" width="32.5" bestFit="1" customWidth="1"/>
@@ -9574,15 +9918,15 @@
     <row r="11" spans="1:5" ht="14.6" thickBot="1">
       <c r="A11" s="17" t="str">
         <f>'Edited additions'!A126</f>
-        <v>00144BC8</v>
+        <v>00148BC8</v>
       </c>
       <c r="B11" s="18" t="str">
         <f>_xlfn.CONCAT('Edited additions'!B126:B127)</f>
-        <v>14009B0302FF3500460103FF3500470103FF35009B0303FF5000F80202FF67009B0303FF6900020102FF69009B0302FF8F00240301FF8F005D0301FFD4009E0203FFD4009B0303FFA000640302FFE8009B0303FFF8009D0202FF7501010302FF7C01AC0202007C01E10002007C01AC0203017C01E10003017D01AD0202007D01E10002007D01AD0203017D01E1000301DA01160302FFDA010E0102FF6102610302FF6F02480302006F02150302006F02480303016F021903030186022002030186023701030186022E01030186029B03030186022002030286023701030286022E01030286029B03030292020A0301FFCD02170303FFCD029B0303FF0903180301FF10039E0301FF20039B03030120039B0303020000000000000000000000000000000000000000</v>
+        <v>14009B0302FF1A006E0302FF1A007C0303FF1A00230302001A00230303013500470103FF35009B0303FF5000F80202FF67009B0303FF6900020102FF69009B0302FF8F00240301FF8F005D0301FFD4009E0203FFD4009B0303FF9A00680302FFA000640302FFE8009B0303FFF8009D0202FF7501010302FF7C01AC0202007C01E10002007C01AC0203017C01E10003017D01AD0202007D01E10002007D01AD0203017D01E1000301DA01160302FFF401780302FF2102830302FF6102610302FF6F02480302006F02150302006F02480303016F021903030186022002030186023701030186022E01030186029B03030186022002030286023701030286022E01030286029B03030292020A0301FF9C02820302FFA6027A0302FFAF02810302FFCD02170303FFCD029B0303FF0903180301FF10039E0301FF20039B03030120039B0303020000000000000000000000000000000000000000</v>
       </c>
       <c r="C11" s="19" t="str">
         <f>DEC2HEX(LEN(B11)/2,3)</f>
-        <v>128</v>
+        <v>158</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="15" thickTop="1" thickBot="1"/>
@@ -9645,13 +9989,13 @@
         <f>'code.bin'!A26</f>
         <v>004B99F0</v>
       </c>
-      <c r="C17" s="8" t="str" cm="1">
-        <f t="array" ref="C17">_xlfn.CONCAT('code.bin'!C26:C42,_xlfn._xlws.FILTER('Table of Ultra Bursts'!I:I,LEN('Table of Ultra Bursts'!I:I)=6),REPT(0,2))</f>
-        <v>04109DE40C002DE934208FE2B030D2E1000053E30000A0030700000A030050E10300001A0230D2E5030051E10100A0030100000A032082E2F3FFFFEA0C00BDE81EFF2FE11400023500035000026700036900028F0001D40003A00002E80003F800027501027C01027C01037D01027D0103DA01026102026F02026F0203860203920201CD020309030110030120030300</v>
+      <c r="C17" s="8" t="str">
+        <f>_xlfn.CONCAT('code.bin'!C26:C42,_xlfn.TEXTJOIN("",TRUE,_xlfn.UNIQUE('Table of Ultra Bursts'!I2:I1048576,FALSE))&amp;REPT(0,4))</f>
+        <v>04109DE40C002DE934208FE2B030D2E1000053E30000A0030700000A030050E10300001A0230D2E5030051E10100A0030100000A032082E2F3FFFFEA0C00BDE81EFF2FE11400021A00021A00033500035000026700036900028F0001D400039A0002A00002E80003F800027501027C01027C01037D01027D0103DA0102F401022102026102026F02026F02038602039202019C0202A60202AF0202CD02030903011003012003030000</v>
       </c>
       <c r="D17" s="9" t="str">
         <f t="shared" si="1"/>
-        <v>090</v>
+        <v>0A9</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -9692,16 +10036,22 @@
         <f>'code.bin'!B26</f>
         <v>004B9A00</v>
       </c>
-      <c r="C20" s="11" t="str" cm="1">
-        <f t="array" ref="C20">_xlfn.CONCAT('code.bin'!D26:D42,_xlfn._xlws.FILTER('Table of Ultra Bursts'!I:I,LEN('Table of Ultra Bursts'!I:I)=6),REPT(0,2))</f>
-        <v>04109DE40C002DE934208FE2B030D2E1000053E30000A0030700000A030050E10300001A0230D2E5030051E10100A0030100000A032082E2F3FFFFEA0C00BDE81EFF2FE11400023500035000026700036900028F0001D40003A00002E80003F800027501027C01027C01037D01027D0103DA01026102026F02026F0203860203920201CD020309030110030120030300</v>
+      <c r="C20" s="11" t="str">
+        <f>_xlfn.CONCAT('code.bin'!D26:D42,_xlfn.TEXTJOIN("",TRUE,_xlfn.UNIQUE('Table of Ultra Bursts'!I2:I1048576,FALSE))&amp;REPT(0,4))</f>
+        <v>04109DE40C002DE934208FE2B030D2E1000053E30000A0030700000A030050E10300001A0230D2E5030051E10100A0030100000A032082E2F3FFFFEA0C00BDE81EFF2FE11400021A00021A00033500035000026700036900028F0001D400039A0002A00002E80003F800027501027C01027C01037D01027D0103DA0102F401022102026102026F02026F02038602039202019C0202A60202AF0202CD02030903011003012003030000</v>
       </c>
       <c r="D20" s="12" t="str">
         <f t="shared" si="1"/>
-        <v>090</v>
+        <v>0A9</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="14.6" thickTop="1"/>
+    <row r="22" spans="1:4">
+      <c r="C22">
+        <f>LEN(C20)</f>
+        <v>338</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A2:C2"/>
@@ -11448,7 +11798,7 @@
         <v>2046</v>
       </c>
       <c r="D48" s="40" t="s">
-        <v>2131</v>
+        <v>2130</v>
       </c>
       <c r="G48" s="27"/>
     </row>
@@ -11464,7 +11814,7 @@
         <v>1242</v>
       </c>
       <c r="D49" s="40" t="s">
-        <v>2129</v>
+        <v>2128</v>
       </c>
       <c r="G49" s="27"/>
     </row>
@@ -11481,7 +11831,7 @@
         <v>bne 0x000FD0CC</v>
       </c>
       <c r="D50" s="40" t="s">
-        <v>2130</v>
+        <v>2129</v>
       </c>
       <c r="G50" s="27"/>
     </row>
@@ -12369,7 +12719,7 @@
         <v>beq 0x000FD190</v>
       </c>
       <c r="D108" s="26" t="s">
-        <v>2295</v>
+        <v>2294</v>
       </c>
       <c r="G108" s="27"/>
     </row>
@@ -12555,15 +12905,15 @@
     </row>
     <row r="126" spans="1:11">
       <c r="A126" s="26" t="s">
-        <v>2128</v>
+        <v>2311</v>
       </c>
       <c r="B126" s="26" t="str" cm="1">
         <f t="array" ref="B126">_xlfn.CONCAT(_xlfn._xlws.FILTER('Table of Ultra Bursts'!H:H,ISNUMBER('Table of Ultra Bursts'!C:C)))</f>
-        <v>14009B0302FF3500460103FF3500470103FF35009B0303FF5000F80202FF67009B0303FF6900020102FF69009B0302FF8F00240301FF8F005D0301FFD4009E0203FFD4009B0303FFA000640302FFE8009B0303FFF8009D0202FF7501010302FF7C01AC0202007C01E10002007C01AC0203017C01E10003017D01AD0202007D01E10002007D01AD0203017D01E1000301DA01160302FFDA010E0102FF6102610302FF6F02480302006F02150302006F02480303016F021903030186022002030186023701030186022E01030186029B03030186022002030286023701030286022E01030286029B03030292020A0301FFCD02170303FFCD029B0303FF0903180301FF10039E0301FF20039B03030120039B030302</v>
+        <v>14009B0302FF1A006E0302FF1A007C0303FF1A00230302001A00230303013500470103FF35009B0303FF5000F80202FF67009B0303FF6900020102FF69009B0302FF8F00240301FF8F005D0301FFD4009E0203FFD4009B0303FF9A00680302FFA000640302FFE8009B0303FFF8009D0202FF7501010302FF7C01AC0202007C01E10002007C01AC0203017C01E10003017D01AD0202007D01E10002007D01AD0203017D01E1000301DA01160302FFF401780302FF2102830302FF6102610302FF6F02480302006F02150302006F02480303016F021903030186022002030186023701030186022E01030186029B03030186022002030286023701030286022E01030286029B03030292020A0301FF9C02820302FFA6027A0302FFAF02810302FFCD02170303FFCD029B0303FF0903180301FF10039E0301FF20039B03030120039B030302</v>
       </c>
       <c r="C126" s="26">
         <f>LEN(B126)</f>
-        <v>552</v>
+        <v>648</v>
       </c>
       <c r="G126" s="27"/>
     </row>
@@ -19250,7 +19600,7 @@
         <v>0071</v>
       </c>
       <c r="C113" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
       <c r="D113" t="str">
         <f t="shared" si="6"/>
@@ -19273,7 +19623,7 @@
         <v>0072</v>
       </c>
       <c r="C114" t="s">
-        <v>2134</v>
+        <v>2133</v>
       </c>
       <c r="D114" t="str">
         <f t="shared" si="6"/>
@@ -19296,7 +19646,7 @@
         <v>0073</v>
       </c>
       <c r="C115" t="s">
-        <v>2135</v>
+        <v>2134</v>
       </c>
       <c r="D115" t="str">
         <f t="shared" si="6"/>
@@ -19411,7 +19761,7 @@
         <v>0078</v>
       </c>
       <c r="C120" t="s">
-        <v>2136</v>
+        <v>2135</v>
       </c>
       <c r="D120" t="str">
         <f t="shared" si="6"/>
@@ -19434,7 +19784,7 @@
         <v>0079</v>
       </c>
       <c r="C121" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="D121" t="str">
         <f t="shared" si="6"/>
@@ -19457,7 +19807,7 @@
         <v>007A</v>
       </c>
       <c r="C122" t="s">
-        <v>2138</v>
+        <v>2137</v>
       </c>
       <c r="D122" t="str">
         <f t="shared" si="6"/>
@@ -19480,7 +19830,7 @@
         <v>007B</v>
       </c>
       <c r="C123" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="D123" t="str">
         <f t="shared" si="6"/>
@@ -19503,7 +19853,7 @@
         <v>007C</v>
       </c>
       <c r="C124" t="s">
-        <v>2140</v>
+        <v>2139</v>
       </c>
       <c r="D124" t="str">
         <f t="shared" si="6"/>
@@ -19526,7 +19876,7 @@
         <v>007D</v>
       </c>
       <c r="C125" t="s">
-        <v>2141</v>
+        <v>2140</v>
       </c>
       <c r="D125" t="str">
         <f t="shared" si="6"/>
@@ -19549,7 +19899,7 @@
         <v>007E</v>
       </c>
       <c r="C126" t="s">
-        <v>2142</v>
+        <v>2141</v>
       </c>
       <c r="D126" t="str">
         <f t="shared" si="6"/>
@@ -19572,7 +19922,7 @@
         <v>007F</v>
       </c>
       <c r="C127" t="s">
-        <v>2143</v>
+        <v>2142</v>
       </c>
       <c r="D127" t="str">
         <f t="shared" si="6"/>
@@ -19595,7 +19945,7 @@
         <v>0080</v>
       </c>
       <c r="C128" t="s">
-        <v>2144</v>
+        <v>2143</v>
       </c>
       <c r="D128" t="str">
         <f t="shared" si="6"/>
@@ -19618,7 +19968,7 @@
         <v>0081</v>
       </c>
       <c r="C129" t="s">
-        <v>2145</v>
+        <v>2144</v>
       </c>
       <c r="D129" t="str">
         <f t="shared" si="6"/>
@@ -19641,7 +19991,7 @@
         <v>0082</v>
       </c>
       <c r="C130" t="s">
-        <v>2146</v>
+        <v>2145</v>
       </c>
       <c r="D130" t="str">
         <f t="shared" si="6"/>
@@ -19664,7 +20014,7 @@
         <v>0083</v>
       </c>
       <c r="C131" t="s">
-        <v>2147</v>
+        <v>2146</v>
       </c>
       <c r="D131" t="str">
         <f t="shared" si="6"/>
@@ -19687,7 +20037,7 @@
         <v>0084</v>
       </c>
       <c r="C132" t="s">
-        <v>2148</v>
+        <v>2147</v>
       </c>
       <c r="D132" t="str">
         <f t="shared" si="6"/>
@@ -19710,7 +20060,7 @@
         <v>0085</v>
       </c>
       <c r="C133" t="s">
-        <v>2149</v>
+        <v>2148</v>
       </c>
       <c r="D133" t="str">
         <f t="shared" si="6"/>
@@ -24195,7 +24545,7 @@
         <v>0148</v>
       </c>
       <c r="C328" t="s">
-        <v>2150</v>
+        <v>2149</v>
       </c>
       <c r="D328" t="str">
         <f t="shared" si="15"/>
@@ -24218,7 +24568,7 @@
         <v>0149</v>
       </c>
       <c r="C329" t="s">
-        <v>2151</v>
+        <v>2150</v>
       </c>
       <c r="D329" t="str">
         <f t="shared" si="15"/>
@@ -24241,7 +24591,7 @@
         <v>014A</v>
       </c>
       <c r="C330" t="s">
-        <v>2152</v>
+        <v>2151</v>
       </c>
       <c r="D330" t="str">
         <f t="shared" si="15"/>
@@ -24264,7 +24614,7 @@
         <v>014B</v>
       </c>
       <c r="C331" t="s">
-        <v>2153</v>
+        <v>2152</v>
       </c>
       <c r="D331" t="str">
         <f t="shared" si="15"/>
@@ -24287,7 +24637,7 @@
         <v>014C</v>
       </c>
       <c r="C332" t="s">
-        <v>2154</v>
+        <v>2153</v>
       </c>
       <c r="D332" t="str">
         <f t="shared" si="15"/>
@@ -24310,7 +24660,7 @@
         <v>014D</v>
       </c>
       <c r="C333" t="s">
-        <v>2155</v>
+        <v>2154</v>
       </c>
       <c r="D333" t="str">
         <f t="shared" si="15"/>
@@ -24333,7 +24683,7 @@
         <v>014E</v>
       </c>
       <c r="C334" t="s">
-        <v>2156</v>
+        <v>2155</v>
       </c>
       <c r="D334" t="str">
         <f t="shared" si="15"/>
@@ -24356,7 +24706,7 @@
         <v>014F</v>
       </c>
       <c r="C335" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="D335" t="str">
         <f t="shared" si="15"/>
@@ -24379,7 +24729,7 @@
         <v>0150</v>
       </c>
       <c r="C336" t="s">
-        <v>2158</v>
+        <v>2157</v>
       </c>
       <c r="D336" t="str">
         <f t="shared" si="15"/>
@@ -24402,7 +24752,7 @@
         <v>0151</v>
       </c>
       <c r="C337" t="s">
-        <v>2159</v>
+        <v>2158</v>
       </c>
       <c r="D337" t="str">
         <f t="shared" si="15"/>
@@ -24425,7 +24775,7 @@
         <v>0152</v>
       </c>
       <c r="C338" t="s">
-        <v>2160</v>
+        <v>2159</v>
       </c>
       <c r="D338" t="str">
         <f t="shared" si="15"/>
@@ -24448,7 +24798,7 @@
         <v>0153</v>
       </c>
       <c r="C339" t="s">
-        <v>2161</v>
+        <v>2160</v>
       </c>
       <c r="D339" t="str">
         <f t="shared" si="15"/>
@@ -24471,7 +24821,7 @@
         <v>0154</v>
       </c>
       <c r="C340" t="s">
-        <v>2162</v>
+        <v>2161</v>
       </c>
       <c r="D340" t="str">
         <f t="shared" si="15"/>
@@ -24494,7 +24844,7 @@
         <v>0155</v>
       </c>
       <c r="C341" t="s">
-        <v>2163</v>
+        <v>2162</v>
       </c>
       <c r="D341" t="str">
         <f t="shared" si="15"/>
@@ -24517,7 +24867,7 @@
         <v>0156</v>
       </c>
       <c r="C342" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="D342" t="str">
         <f t="shared" si="15"/>
@@ -24540,7 +24890,7 @@
         <v>0157</v>
       </c>
       <c r="C343" t="s">
-        <v>2165</v>
+        <v>2164</v>
       </c>
       <c r="D343" t="str">
         <f t="shared" si="15"/>
@@ -24563,7 +24913,7 @@
         <v>0158</v>
       </c>
       <c r="C344" t="s">
-        <v>2166</v>
+        <v>2165</v>
       </c>
       <c r="D344" t="str">
         <f t="shared" si="15"/>
@@ -24586,7 +24936,7 @@
         <v>0159</v>
       </c>
       <c r="C345" t="s">
-        <v>2167</v>
+        <v>2166</v>
       </c>
       <c r="D345" t="str">
         <f t="shared" si="15"/>
@@ -24609,7 +24959,7 @@
         <v>015A</v>
       </c>
       <c r="C346" t="s">
-        <v>2168</v>
+        <v>2167</v>
       </c>
       <c r="D346" t="str">
         <f t="shared" si="15"/>
@@ -24632,7 +24982,7 @@
         <v>015B</v>
       </c>
       <c r="C347" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
       <c r="D347" t="str">
         <f t="shared" si="15"/>
@@ -24655,7 +25005,7 @@
         <v>015C</v>
       </c>
       <c r="C348" t="s">
-        <v>2170</v>
+        <v>2169</v>
       </c>
       <c r="D348" t="str">
         <f t="shared" si="15"/>
@@ -24678,7 +25028,7 @@
         <v>015D</v>
       </c>
       <c r="C349" t="s">
-        <v>2171</v>
+        <v>2170</v>
       </c>
       <c r="D349" t="str">
         <f t="shared" si="15"/>
@@ -24701,7 +25051,7 @@
         <v>015E</v>
       </c>
       <c r="C350" t="s">
-        <v>2172</v>
+        <v>2171</v>
       </c>
       <c r="D350" t="str">
         <f t="shared" si="15"/>
@@ -24724,7 +25074,7 @@
         <v>015F</v>
       </c>
       <c r="C351" t="s">
-        <v>2173</v>
+        <v>2172</v>
       </c>
       <c r="D351" t="str">
         <f t="shared" si="15"/>
@@ -24747,7 +25097,7 @@
         <v>0160</v>
       </c>
       <c r="C352" t="s">
-        <v>2174</v>
+        <v>2173</v>
       </c>
       <c r="D352" t="str">
         <f t="shared" si="15"/>
@@ -24770,7 +25120,7 @@
         <v>0161</v>
       </c>
       <c r="C353" t="s">
-        <v>2175</v>
+        <v>2174</v>
       </c>
       <c r="D353" t="str">
         <f t="shared" si="15"/>
@@ -24793,7 +25143,7 @@
         <v>0162</v>
       </c>
       <c r="C354" t="s">
-        <v>2176</v>
+        <v>2175</v>
       </c>
       <c r="D354" t="str">
         <f t="shared" si="15"/>
@@ -24816,7 +25166,7 @@
         <v>0163</v>
       </c>
       <c r="C355" t="s">
-        <v>2177</v>
+        <v>2176</v>
       </c>
       <c r="D355" t="str">
         <f t="shared" si="15"/>
@@ -24839,7 +25189,7 @@
         <v>0164</v>
       </c>
       <c r="C356" t="s">
-        <v>2178</v>
+        <v>2177</v>
       </c>
       <c r="D356" t="str">
         <f t="shared" si="15"/>
@@ -24862,7 +25212,7 @@
         <v>0165</v>
       </c>
       <c r="C357" t="s">
-        <v>2179</v>
+        <v>2178</v>
       </c>
       <c r="D357" t="str">
         <f t="shared" ref="D357:D420" si="18">RIGHT(B357,2)&amp;LEFT(B357,2)</f>
@@ -24885,7 +25235,7 @@
         <v>0166</v>
       </c>
       <c r="C358" t="s">
-        <v>2180</v>
+        <v>2179</v>
       </c>
       <c r="D358" t="str">
         <f t="shared" si="18"/>
@@ -24908,7 +25258,7 @@
         <v>0167</v>
       </c>
       <c r="C359" t="s">
-        <v>2181</v>
+        <v>2180</v>
       </c>
       <c r="D359" t="str">
         <f t="shared" si="18"/>
@@ -24931,7 +25281,7 @@
         <v>0168</v>
       </c>
       <c r="C360" t="s">
-        <v>2182</v>
+        <v>2181</v>
       </c>
       <c r="D360" t="str">
         <f t="shared" si="18"/>
@@ -24954,7 +25304,7 @@
         <v>0169</v>
       </c>
       <c r="C361" t="s">
-        <v>2183</v>
+        <v>2182</v>
       </c>
       <c r="D361" t="str">
         <f t="shared" si="18"/>
@@ -24977,7 +25327,7 @@
         <v>016A</v>
       </c>
       <c r="C362" t="s">
-        <v>2184</v>
+        <v>2183</v>
       </c>
       <c r="D362" t="str">
         <f t="shared" si="18"/>
@@ -25000,7 +25350,7 @@
         <v>016B</v>
       </c>
       <c r="C363" t="s">
-        <v>2185</v>
+        <v>2184</v>
       </c>
       <c r="D363" t="str">
         <f t="shared" si="18"/>
@@ -25023,7 +25373,7 @@
         <v>016C</v>
       </c>
       <c r="C364" t="s">
-        <v>2186</v>
+        <v>2185</v>
       </c>
       <c r="D364" t="str">
         <f t="shared" si="18"/>
@@ -25046,7 +25396,7 @@
         <v>016D</v>
       </c>
       <c r="C365" t="s">
-        <v>2187</v>
+        <v>2186</v>
       </c>
       <c r="D365" t="str">
         <f t="shared" si="18"/>
@@ -25069,7 +25419,7 @@
         <v>016E</v>
       </c>
       <c r="C366" t="s">
-        <v>2188</v>
+        <v>2187</v>
       </c>
       <c r="D366" t="str">
         <f t="shared" si="18"/>
@@ -25092,7 +25442,7 @@
         <v>016F</v>
       </c>
       <c r="C367" t="s">
-        <v>2189</v>
+        <v>2188</v>
       </c>
       <c r="D367" t="str">
         <f t="shared" si="18"/>
@@ -25115,7 +25465,7 @@
         <v>0170</v>
       </c>
       <c r="C368" t="s">
-        <v>2190</v>
+        <v>2189</v>
       </c>
       <c r="D368" t="str">
         <f t="shared" si="18"/>
@@ -25138,7 +25488,7 @@
         <v>0171</v>
       </c>
       <c r="C369" t="s">
-        <v>2191</v>
+        <v>2190</v>
       </c>
       <c r="D369" t="str">
         <f t="shared" si="18"/>
@@ -25161,7 +25511,7 @@
         <v>0172</v>
       </c>
       <c r="C370" t="s">
-        <v>2192</v>
+        <v>2191</v>
       </c>
       <c r="D370" t="str">
         <f t="shared" si="18"/>
@@ -25184,7 +25534,7 @@
         <v>0173</v>
       </c>
       <c r="C371" t="s">
-        <v>2193</v>
+        <v>2192</v>
       </c>
       <c r="D371" t="str">
         <f t="shared" si="18"/>
@@ -25207,7 +25557,7 @@
         <v>0174</v>
       </c>
       <c r="C372" t="s">
-        <v>2194</v>
+        <v>2193</v>
       </c>
       <c r="D372" t="str">
         <f t="shared" si="18"/>
@@ -25230,7 +25580,7 @@
         <v>0175</v>
       </c>
       <c r="C373" t="s">
-        <v>2195</v>
+        <v>2194</v>
       </c>
       <c r="D373" t="str">
         <f t="shared" si="18"/>
@@ -25253,7 +25603,7 @@
         <v>0176</v>
       </c>
       <c r="C374" t="s">
-        <v>2196</v>
+        <v>2195</v>
       </c>
       <c r="D374" t="str">
         <f t="shared" si="18"/>
@@ -25276,7 +25626,7 @@
         <v>0177</v>
       </c>
       <c r="C375" t="s">
-        <v>2197</v>
+        <v>2196</v>
       </c>
       <c r="D375" t="str">
         <f t="shared" si="18"/>
@@ -25299,7 +25649,7 @@
         <v>0178</v>
       </c>
       <c r="C376" t="s">
-        <v>2198</v>
+        <v>2197</v>
       </c>
       <c r="D376" t="str">
         <f t="shared" si="18"/>
@@ -25322,7 +25672,7 @@
         <v>0179</v>
       </c>
       <c r="C377" t="s">
-        <v>2199</v>
+        <v>2198</v>
       </c>
       <c r="D377" t="str">
         <f t="shared" si="18"/>
@@ -25345,7 +25695,7 @@
         <v>017A</v>
       </c>
       <c r="C378" t="s">
-        <v>2200</v>
+        <v>2199</v>
       </c>
       <c r="D378" t="str">
         <f t="shared" si="18"/>
@@ -25368,7 +25718,7 @@
         <v>017B</v>
       </c>
       <c r="C379" t="s">
-        <v>2201</v>
+        <v>2200</v>
       </c>
       <c r="D379" t="str">
         <f t="shared" si="18"/>
@@ -25391,7 +25741,7 @@
         <v>017C</v>
       </c>
       <c r="C380" t="s">
-        <v>2202</v>
+        <v>2201</v>
       </c>
       <c r="D380" t="str">
         <f t="shared" si="18"/>
@@ -25414,7 +25764,7 @@
         <v>017D</v>
       </c>
       <c r="C381" t="s">
-        <v>2203</v>
+        <v>2202</v>
       </c>
       <c r="D381" t="str">
         <f t="shared" si="18"/>
@@ -25437,7 +25787,7 @@
         <v>017E</v>
       </c>
       <c r="C382" t="s">
-        <v>2204</v>
+        <v>2203</v>
       </c>
       <c r="D382" t="str">
         <f t="shared" si="18"/>
@@ -25460,7 +25810,7 @@
         <v>017F</v>
       </c>
       <c r="C383" t="s">
-        <v>2205</v>
+        <v>2204</v>
       </c>
       <c r="D383" t="str">
         <f t="shared" si="18"/>
@@ -25483,7 +25833,7 @@
         <v>0180</v>
       </c>
       <c r="C384" t="s">
-        <v>2206</v>
+        <v>2205</v>
       </c>
       <c r="D384" t="str">
         <f t="shared" si="18"/>
@@ -25506,7 +25856,7 @@
         <v>0181</v>
       </c>
       <c r="C385" t="s">
-        <v>2207</v>
+        <v>2206</v>
       </c>
       <c r="D385" t="str">
         <f t="shared" si="18"/>
@@ -25529,7 +25879,7 @@
         <v>0182</v>
       </c>
       <c r="C386" t="s">
-        <v>2208</v>
+        <v>2207</v>
       </c>
       <c r="D386" t="str">
         <f t="shared" si="18"/>
@@ -25552,7 +25902,7 @@
         <v>0183</v>
       </c>
       <c r="C387" t="s">
-        <v>2209</v>
+        <v>2208</v>
       </c>
       <c r="D387" t="str">
         <f t="shared" si="18"/>
@@ -25575,7 +25925,7 @@
         <v>0184</v>
       </c>
       <c r="C388" t="s">
-        <v>2210</v>
+        <v>2209</v>
       </c>
       <c r="D388" t="str">
         <f t="shared" si="18"/>
@@ -25598,7 +25948,7 @@
         <v>0185</v>
       </c>
       <c r="C389" t="s">
-        <v>2211</v>
+        <v>2210</v>
       </c>
       <c r="D389" t="str">
         <f t="shared" si="18"/>
@@ -25621,7 +25971,7 @@
         <v>0186</v>
       </c>
       <c r="C390" t="s">
-        <v>2212</v>
+        <v>2211</v>
       </c>
       <c r="D390" t="str">
         <f t="shared" si="18"/>
@@ -25644,7 +25994,7 @@
         <v>0187</v>
       </c>
       <c r="C391" t="s">
-        <v>2213</v>
+        <v>2212</v>
       </c>
       <c r="D391" t="str">
         <f t="shared" si="18"/>
@@ -25667,7 +26017,7 @@
         <v>0188</v>
       </c>
       <c r="C392" t="s">
-        <v>2214</v>
+        <v>2213</v>
       </c>
       <c r="D392" t="str">
         <f t="shared" si="18"/>
@@ -25690,7 +26040,7 @@
         <v>0189</v>
       </c>
       <c r="C393" t="s">
-        <v>2215</v>
+        <v>2214</v>
       </c>
       <c r="D393" t="str">
         <f t="shared" si="18"/>
@@ -25713,7 +26063,7 @@
         <v>018A</v>
       </c>
       <c r="C394" t="s">
-        <v>2216</v>
+        <v>2215</v>
       </c>
       <c r="D394" t="str">
         <f t="shared" si="18"/>
@@ -25736,7 +26086,7 @@
         <v>018B</v>
       </c>
       <c r="C395" t="s">
-        <v>2217</v>
+        <v>2216</v>
       </c>
       <c r="D395" t="str">
         <f t="shared" si="18"/>
@@ -25759,7 +26109,7 @@
         <v>018C</v>
       </c>
       <c r="C396" t="s">
-        <v>2218</v>
+        <v>2217</v>
       </c>
       <c r="D396" t="str">
         <f t="shared" si="18"/>
@@ -25782,7 +26132,7 @@
         <v>018D</v>
       </c>
       <c r="C397" t="s">
-        <v>2219</v>
+        <v>2218</v>
       </c>
       <c r="D397" t="str">
         <f t="shared" si="18"/>
@@ -25805,7 +26155,7 @@
         <v>018E</v>
       </c>
       <c r="C398" t="s">
-        <v>2220</v>
+        <v>2219</v>
       </c>
       <c r="D398" t="str">
         <f t="shared" si="18"/>
@@ -25828,7 +26178,7 @@
         <v>018F</v>
       </c>
       <c r="C399" t="s">
-        <v>2221</v>
+        <v>2220</v>
       </c>
       <c r="D399" t="str">
         <f t="shared" si="18"/>
@@ -25851,7 +26201,7 @@
         <v>0190</v>
       </c>
       <c r="C400" t="s">
-        <v>2222</v>
+        <v>2221</v>
       </c>
       <c r="D400" t="str">
         <f t="shared" si="18"/>
@@ -25874,7 +26224,7 @@
         <v>0191</v>
       </c>
       <c r="C401" t="s">
-        <v>2223</v>
+        <v>2222</v>
       </c>
       <c r="D401" t="str">
         <f t="shared" si="18"/>
@@ -25897,7 +26247,7 @@
         <v>0192</v>
       </c>
       <c r="C402" t="s">
-        <v>2224</v>
+        <v>2223</v>
       </c>
       <c r="D402" t="str">
         <f t="shared" si="18"/>
@@ -25920,7 +26270,7 @@
         <v>0193</v>
       </c>
       <c r="C403" t="s">
-        <v>2225</v>
+        <v>2224</v>
       </c>
       <c r="D403" t="str">
         <f t="shared" si="18"/>
@@ -25943,7 +26293,7 @@
         <v>0194</v>
       </c>
       <c r="C404" t="s">
-        <v>2226</v>
+        <v>2225</v>
       </c>
       <c r="D404" t="str">
         <f t="shared" si="18"/>
@@ -25966,7 +26316,7 @@
         <v>0195</v>
       </c>
       <c r="C405" t="s">
-        <v>2227</v>
+        <v>2226</v>
       </c>
       <c r="D405" t="str">
         <f t="shared" si="18"/>
@@ -25989,7 +26339,7 @@
         <v>0196</v>
       </c>
       <c r="C406" t="s">
-        <v>2228</v>
+        <v>2227</v>
       </c>
       <c r="D406" t="str">
         <f t="shared" si="18"/>
@@ -26012,7 +26362,7 @@
         <v>0197</v>
       </c>
       <c r="C407" t="s">
-        <v>2229</v>
+        <v>2228</v>
       </c>
       <c r="D407" t="str">
         <f t="shared" si="18"/>
@@ -26035,7 +26385,7 @@
         <v>0198</v>
       </c>
       <c r="C408" t="s">
-        <v>2230</v>
+        <v>2229</v>
       </c>
       <c r="D408" t="str">
         <f t="shared" si="18"/>
@@ -26058,7 +26408,7 @@
         <v>0199</v>
       </c>
       <c r="C409" t="s">
-        <v>2231</v>
+        <v>2230</v>
       </c>
       <c r="D409" t="str">
         <f t="shared" si="18"/>
@@ -26081,7 +26431,7 @@
         <v>019A</v>
       </c>
       <c r="C410" t="s">
-        <v>2232</v>
+        <v>2231</v>
       </c>
       <c r="D410" t="str">
         <f t="shared" si="18"/>
@@ -26104,7 +26454,7 @@
         <v>019B</v>
       </c>
       <c r="C411" t="s">
-        <v>2233</v>
+        <v>2232</v>
       </c>
       <c r="D411" t="str">
         <f t="shared" si="18"/>
@@ -26127,7 +26477,7 @@
         <v>019C</v>
       </c>
       <c r="C412" t="s">
-        <v>2234</v>
+        <v>2233</v>
       </c>
       <c r="D412" t="str">
         <f t="shared" si="18"/>
@@ -26150,7 +26500,7 @@
         <v>019D</v>
       </c>
       <c r="C413" t="s">
-        <v>2235</v>
+        <v>2234</v>
       </c>
       <c r="D413" t="str">
         <f t="shared" si="18"/>
@@ -26173,7 +26523,7 @@
         <v>019E</v>
       </c>
       <c r="C414" t="s">
-        <v>2236</v>
+        <v>2235</v>
       </c>
       <c r="D414" t="str">
         <f t="shared" si="18"/>
@@ -26196,7 +26546,7 @@
         <v>019F</v>
       </c>
       <c r="C415" t="s">
-        <v>2237</v>
+        <v>2236</v>
       </c>
       <c r="D415" t="str">
         <f t="shared" si="18"/>
@@ -26219,7 +26569,7 @@
         <v>01A0</v>
       </c>
       <c r="C416" t="s">
-        <v>2238</v>
+        <v>2237</v>
       </c>
       <c r="D416" t="str">
         <f t="shared" si="18"/>
@@ -26242,7 +26592,7 @@
         <v>01A1</v>
       </c>
       <c r="C417" t="s">
-        <v>2239</v>
+        <v>2238</v>
       </c>
       <c r="D417" t="str">
         <f t="shared" si="18"/>
@@ -26265,7 +26615,7 @@
         <v>01A2</v>
       </c>
       <c r="C418" t="s">
-        <v>2240</v>
+        <v>2239</v>
       </c>
       <c r="D418" t="str">
         <f t="shared" si="18"/>
@@ -26288,7 +26638,7 @@
         <v>01A3</v>
       </c>
       <c r="C419" t="s">
-        <v>2241</v>
+        <v>2240</v>
       </c>
       <c r="D419" t="str">
         <f t="shared" si="18"/>
@@ -26311,7 +26661,7 @@
         <v>01A4</v>
       </c>
       <c r="C420" t="s">
-        <v>2242</v>
+        <v>2241</v>
       </c>
       <c r="D420" t="str">
         <f t="shared" si="18"/>
@@ -26334,7 +26684,7 @@
         <v>01A5</v>
       </c>
       <c r="C421" t="s">
-        <v>2243</v>
+        <v>2242</v>
       </c>
       <c r="D421" t="str">
         <f t="shared" ref="D421:D484" si="21">RIGHT(B421,2)&amp;LEFT(B421,2)</f>
@@ -26357,7 +26707,7 @@
         <v>01A6</v>
       </c>
       <c r="C422" t="s">
-        <v>2244</v>
+        <v>2243</v>
       </c>
       <c r="D422" t="str">
         <f t="shared" si="21"/>
@@ -26380,7 +26730,7 @@
         <v>01A7</v>
       </c>
       <c r="C423" t="s">
-        <v>2245</v>
+        <v>2244</v>
       </c>
       <c r="D423" t="str">
         <f t="shared" si="21"/>
@@ -26403,7 +26753,7 @@
         <v>01A8</v>
       </c>
       <c r="C424" t="s">
-        <v>2246</v>
+        <v>2245</v>
       </c>
       <c r="D424" t="str">
         <f t="shared" si="21"/>
@@ -26426,7 +26776,7 @@
         <v>01A9</v>
       </c>
       <c r="C425" t="s">
-        <v>2247</v>
+        <v>2246</v>
       </c>
       <c r="D425" t="str">
         <f t="shared" si="21"/>
@@ -26449,7 +26799,7 @@
         <v>01AA</v>
       </c>
       <c r="C426" t="s">
-        <v>2248</v>
+        <v>2247</v>
       </c>
       <c r="D426" t="str">
         <f t="shared" si="21"/>
@@ -26472,7 +26822,7 @@
         <v>01AB</v>
       </c>
       <c r="C427" t="s">
-        <v>2249</v>
+        <v>2248</v>
       </c>
       <c r="D427" t="str">
         <f t="shared" si="21"/>
@@ -30865,7 +31215,7 @@
         <v>026A</v>
       </c>
       <c r="C618" t="s">
-        <v>2250</v>
+        <v>2249</v>
       </c>
       <c r="D618" t="str">
         <f t="shared" si="30"/>
@@ -30888,7 +31238,7 @@
         <v>026B</v>
       </c>
       <c r="C619" t="s">
-        <v>2251</v>
+        <v>2250</v>
       </c>
       <c r="D619" t="str">
         <f t="shared" si="30"/>
@@ -30911,7 +31261,7 @@
         <v>026C</v>
       </c>
       <c r="C620" t="s">
-        <v>2252</v>
+        <v>2251</v>
       </c>
       <c r="D620" t="str">
         <f t="shared" si="30"/>
@@ -32521,7 +32871,7 @@
         <v>02B2</v>
       </c>
       <c r="C690" t="s">
-        <v>2253</v>
+        <v>2252</v>
       </c>
       <c r="D690" t="str">
         <f t="shared" si="33"/>
@@ -32544,7 +32894,7 @@
         <v>02B3</v>
       </c>
       <c r="C691" t="s">
-        <v>2254</v>
+        <v>2253</v>
       </c>
       <c r="D691" t="str">
         <f t="shared" si="33"/>
@@ -32567,7 +32917,7 @@
         <v>02B4</v>
       </c>
       <c r="C692" t="s">
-        <v>2255</v>
+        <v>2254</v>
       </c>
       <c r="D692" t="str">
         <f t="shared" si="33"/>
@@ -32590,7 +32940,7 @@
         <v>02B5</v>
       </c>
       <c r="C693" t="s">
-        <v>2256</v>
+        <v>2255</v>
       </c>
       <c r="D693" t="str">
         <f t="shared" si="33"/>
@@ -33602,7 +33952,7 @@
         <v>02E1</v>
       </c>
       <c r="C737" t="s">
-        <v>2257</v>
+        <v>2256</v>
       </c>
       <c r="D737" t="str">
         <f t="shared" si="33"/>
@@ -35527,7 +35877,7 @@
         <v>0339</v>
       </c>
       <c r="C825" t="s">
-        <v>2258</v>
+        <v>2257</v>
       </c>
       <c r="D825" t="str">
         <f t="shared" si="39"/>
@@ -35544,7 +35894,7 @@
         <v>033A</v>
       </c>
       <c r="C826" t="s">
-        <v>2259</v>
+        <v>2258</v>
       </c>
       <c r="D826" t="str">
         <f t="shared" si="39"/>
@@ -35561,7 +35911,7 @@
         <v>033B</v>
       </c>
       <c r="C827" t="s">
-        <v>2260</v>
+        <v>2259</v>
       </c>
       <c r="D827" t="str">
         <f t="shared" si="39"/>
@@ -35578,7 +35928,7 @@
         <v>033C</v>
       </c>
       <c r="C828" t="s">
-        <v>2261</v>
+        <v>2260</v>
       </c>
       <c r="D828" t="str">
         <f t="shared" si="39"/>
@@ -35595,7 +35945,7 @@
         <v>033D</v>
       </c>
       <c r="C829" t="s">
-        <v>2262</v>
+        <v>2261</v>
       </c>
       <c r="D829" t="str">
         <f t="shared" si="39"/>
@@ -35612,7 +35962,7 @@
         <v>033E</v>
       </c>
       <c r="C830" t="s">
-        <v>2263</v>
+        <v>2262</v>
       </c>
       <c r="D830" t="str">
         <f t="shared" si="39"/>
@@ -35629,7 +35979,7 @@
         <v>033F</v>
       </c>
       <c r="C831" t="s">
-        <v>2264</v>
+        <v>2263</v>
       </c>
       <c r="D831" t="str">
         <f t="shared" si="39"/>
@@ -35646,7 +35996,7 @@
         <v>0340</v>
       </c>
       <c r="C832" t="s">
-        <v>2265</v>
+        <v>2264</v>
       </c>
       <c r="D832" t="str">
         <f t="shared" si="39"/>
@@ -35663,7 +36013,7 @@
         <v>0341</v>
       </c>
       <c r="C833" t="s">
-        <v>2266</v>
+        <v>2265</v>
       </c>
       <c r="D833" t="str">
         <f t="shared" si="39"/>
@@ -35680,7 +36030,7 @@
         <v>0342</v>
       </c>
       <c r="C834" t="s">
-        <v>2267</v>
+        <v>2266</v>
       </c>
       <c r="D834" t="str">
         <f t="shared" si="39"/>
@@ -35697,7 +36047,7 @@
         <v>0343</v>
       </c>
       <c r="C835" t="s">
-        <v>2268</v>
+        <v>2267</v>
       </c>
       <c r="D835" t="str">
         <f t="shared" si="39"/>
@@ -35731,7 +36081,7 @@
         <v>0345</v>
       </c>
       <c r="C837" t="s">
-        <v>2269</v>
+        <v>2268</v>
       </c>
       <c r="D837" t="str">
         <f t="shared" si="39"/>
@@ -35748,7 +36098,7 @@
         <v>0346</v>
       </c>
       <c r="C838" t="s">
-        <v>2270</v>
+        <v>2269</v>
       </c>
       <c r="D838" t="str">
         <f t="shared" si="39"/>
@@ -35765,7 +36115,7 @@
         <v>0347</v>
       </c>
       <c r="C839" t="s">
-        <v>2271</v>
+        <v>2270</v>
       </c>
       <c r="D839" t="str">
         <f t="shared" si="39"/>
@@ -35782,7 +36132,7 @@
         <v>0348</v>
       </c>
       <c r="C840" t="s">
-        <v>2272</v>
+        <v>2271</v>
       </c>
       <c r="D840" t="str">
         <f t="shared" si="39"/>
@@ -35918,7 +36268,7 @@
         <v>0350</v>
       </c>
       <c r="C848" t="s">
-        <v>2283</v>
+        <v>2282</v>
       </c>
       <c r="D848" t="str">
         <f t="shared" si="39"/>
@@ -36105,7 +36455,7 @@
         <v>035B</v>
       </c>
       <c r="C859" t="s">
-        <v>2284</v>
+        <v>2283</v>
       </c>
       <c r="D859" t="str">
         <f t="shared" si="39"/>
@@ -36139,7 +36489,7 @@
         <v>035D</v>
       </c>
       <c r="C861" t="s">
-        <v>2132</v>
+        <v>2131</v>
       </c>
       <c r="D861" t="str">
         <f t="shared" si="39"/>
@@ -36156,7 +36506,7 @@
         <v>035E</v>
       </c>
       <c r="C862" t="s">
-        <v>2285</v>
+        <v>2284</v>
       </c>
       <c r="D862" t="str">
         <f t="shared" si="39"/>
@@ -36173,7 +36523,7 @@
         <v>035F</v>
       </c>
       <c r="C863" t="s">
-        <v>2286</v>
+        <v>2285</v>
       </c>
       <c r="D863" t="str">
         <f t="shared" si="39"/>
@@ -36190,7 +36540,7 @@
         <v>0360</v>
       </c>
       <c r="C864" t="s">
-        <v>2287</v>
+        <v>2286</v>
       </c>
       <c r="D864" t="str">
         <f t="shared" si="39"/>
@@ -36207,7 +36557,7 @@
         <v>0361</v>
       </c>
       <c r="C865" t="s">
-        <v>2288</v>
+        <v>2287</v>
       </c>
       <c r="D865" t="str">
         <f t="shared" si="39"/>
@@ -36224,7 +36574,7 @@
         <v>0362</v>
       </c>
       <c r="C866" t="s">
-        <v>2289</v>
+        <v>2288</v>
       </c>
       <c r="D866" t="str">
         <f t="shared" si="39"/>
@@ -36241,7 +36591,7 @@
         <v>0363</v>
       </c>
       <c r="C867" t="s">
-        <v>2290</v>
+        <v>2289</v>
       </c>
       <c r="D867" t="str">
         <f t="shared" si="39"/>
@@ -36258,7 +36608,7 @@
         <v>0364</v>
       </c>
       <c r="C868" t="s">
-        <v>2291</v>
+        <v>2290</v>
       </c>
       <c r="D868" t="str">
         <f t="shared" si="39"/>
@@ -36275,7 +36625,7 @@
         <v>0365</v>
       </c>
       <c r="C869" t="s">
-        <v>2292</v>
+        <v>2291</v>
       </c>
       <c r="D869" t="str">
         <f t="shared" ref="D869:D932" si="42">RIGHT(B869,2)&amp;LEFT(B869,2)</f>
@@ -36292,7 +36642,7 @@
         <v>0366</v>
       </c>
       <c r="C870" t="s">
-        <v>2293</v>
+        <v>2292</v>
       </c>
       <c r="D870" t="str">
         <f t="shared" si="42"/>
@@ -36309,7 +36659,7 @@
         <v>0367</v>
       </c>
       <c r="C871" t="s">
-        <v>2294</v>
+        <v>2293</v>
       </c>
       <c r="D871" t="str">
         <f t="shared" si="42"/>
@@ -36326,7 +36676,7 @@
         <v>0368</v>
       </c>
       <c r="C872" t="s">
-        <v>1398</v>
+        <v>2296</v>
       </c>
       <c r="D872" t="str">
         <f t="shared" si="42"/>
@@ -36343,7 +36693,7 @@
         <v>0369</v>
       </c>
       <c r="C873" t="s">
-        <v>1398</v>
+        <v>2297</v>
       </c>
       <c r="D873" t="str">
         <f t="shared" si="42"/>
@@ -36360,7 +36710,7 @@
         <v>036A</v>
       </c>
       <c r="C874" t="s">
-        <v>1398</v>
+        <v>2298</v>
       </c>
       <c r="D874" t="str">
         <f t="shared" si="42"/>
@@ -36377,7 +36727,7 @@
         <v>036B</v>
       </c>
       <c r="C875" t="s">
-        <v>1398</v>
+        <v>2299</v>
       </c>
       <c r="D875" t="str">
         <f t="shared" si="42"/>
@@ -36394,7 +36744,7 @@
         <v>036C</v>
       </c>
       <c r="C876" t="s">
-        <v>1398</v>
+        <v>2300</v>
       </c>
       <c r="D876" t="str">
         <f t="shared" si="42"/>
@@ -36411,7 +36761,7 @@
         <v>036D</v>
       </c>
       <c r="C877" t="s">
-        <v>1398</v>
+        <v>2301</v>
       </c>
       <c r="D877" t="str">
         <f t="shared" si="42"/>
@@ -36428,7 +36778,7 @@
         <v>036E</v>
       </c>
       <c r="C878" t="s">
-        <v>1398</v>
+        <v>2309</v>
       </c>
       <c r="D878" t="str">
         <f t="shared" si="42"/>
@@ -36547,7 +36897,7 @@
         <v>0375</v>
       </c>
       <c r="C885" t="s">
-        <v>1398</v>
+        <v>2302</v>
       </c>
       <c r="D885" t="str">
         <f t="shared" si="42"/>
@@ -36564,7 +36914,7 @@
         <v>0376</v>
       </c>
       <c r="C886" t="s">
-        <v>1398</v>
+        <v>2303</v>
       </c>
       <c r="D886" t="str">
         <f t="shared" si="42"/>
@@ -36581,7 +36931,7 @@
         <v>0377</v>
       </c>
       <c r="C887" t="s">
-        <v>1398</v>
+        <v>2304</v>
       </c>
       <c r="D887" t="str">
         <f t="shared" si="42"/>
@@ -36598,7 +36948,7 @@
         <v>0378</v>
       </c>
       <c r="C888" t="s">
-        <v>1398</v>
+        <v>2305</v>
       </c>
       <c r="D888" t="str">
         <f t="shared" si="42"/>
@@ -36615,7 +36965,7 @@
         <v>0379</v>
       </c>
       <c r="C889" t="s">
-        <v>1398</v>
+        <v>2306</v>
       </c>
       <c r="D889" t="str">
         <f t="shared" si="42"/>
@@ -36632,7 +36982,7 @@
         <v>037A</v>
       </c>
       <c r="C890" t="s">
-        <v>1398</v>
+        <v>2307</v>
       </c>
       <c r="D890" t="str">
         <f t="shared" si="42"/>
@@ -36649,7 +36999,7 @@
         <v>037B</v>
       </c>
       <c r="C891" t="s">
-        <v>1398</v>
+        <v>2308</v>
       </c>
       <c r="D891" t="str">
         <f t="shared" si="42"/>
@@ -36666,7 +37016,7 @@
         <v>037C</v>
       </c>
       <c r="C892" t="s">
-        <v>1398</v>
+        <v>2310</v>
       </c>
       <c r="D892" t="str">
         <f t="shared" si="42"/>
@@ -36683,7 +37033,7 @@
         <v>037D</v>
       </c>
       <c r="C893" t="s">
-        <v>1398</v>
+        <v>2312</v>
       </c>
       <c r="D893" t="str">
         <f t="shared" si="42"/>
@@ -36700,7 +37050,7 @@
         <v>037E</v>
       </c>
       <c r="C894" t="s">
-        <v>1398</v>
+        <v>2313</v>
       </c>
       <c r="D894" t="str">
         <f t="shared" si="42"/>
@@ -36717,7 +37067,7 @@
         <v>037F</v>
       </c>
       <c r="C895" t="s">
-        <v>1398</v>
+        <v>2314</v>
       </c>
       <c r="D895" t="str">
         <f t="shared" si="42"/>
@@ -36734,7 +37084,7 @@
         <v>0380</v>
       </c>
       <c r="C896" t="s">
-        <v>1398</v>
+        <v>2315</v>
       </c>
       <c r="D896" t="str">
         <f t="shared" si="42"/>
@@ -36751,7 +37101,7 @@
         <v>0381</v>
       </c>
       <c r="C897" t="s">
-        <v>1398</v>
+        <v>2316</v>
       </c>
       <c r="D897" t="str">
         <f t="shared" si="42"/>
@@ -36768,7 +37118,7 @@
         <v>0382</v>
       </c>
       <c r="C898" t="s">
-        <v>1398</v>
+        <v>2317</v>
       </c>
       <c r="D898" t="str">
         <f t="shared" si="42"/>
@@ -36785,7 +37135,7 @@
         <v>0383</v>
       </c>
       <c r="C899" t="s">
-        <v>1398</v>
+        <v>2318</v>
       </c>
       <c r="D899" t="str">
         <f t="shared" si="42"/>
@@ -36802,7 +37152,7 @@
         <v>0384</v>
       </c>
       <c r="C900" t="s">
-        <v>1398</v>
+        <v>2319</v>
       </c>
       <c r="D900" t="str">
         <f t="shared" si="42"/>
@@ -36819,7 +37169,7 @@
         <v>0385</v>
       </c>
       <c r="C901" t="s">
-        <v>1398</v>
+        <v>2320</v>
       </c>
       <c r="D901" t="str">
         <f t="shared" si="42"/>
@@ -37312,7 +37662,7 @@
         <v>03A2</v>
       </c>
       <c r="C930" t="s">
-        <v>2273</v>
+        <v>2272</v>
       </c>
       <c r="D930" t="str">
         <f t="shared" si="42"/>
@@ -37329,7 +37679,7 @@
         <v>03A3</v>
       </c>
       <c r="C931" t="s">
-        <v>2274</v>
+        <v>2273</v>
       </c>
       <c r="D931" t="str">
         <f t="shared" si="42"/>
@@ -37346,7 +37696,7 @@
         <v>03A4</v>
       </c>
       <c r="C932" t="s">
-        <v>2275</v>
+        <v>2274</v>
       </c>
       <c r="D932" t="str">
         <f t="shared" si="42"/>
@@ -37822,7 +38172,7 @@
         <v>03C0</v>
       </c>
       <c r="C960" t="s">
-        <v>2276</v>
+        <v>2275</v>
       </c>
       <c r="D960" t="str">
         <f t="shared" si="45"/>
@@ -37839,7 +38189,7 @@
         <v>03C1</v>
       </c>
       <c r="C961" t="s">
-        <v>2277</v>
+        <v>2276</v>
       </c>
       <c r="D961" t="str">
         <f t="shared" si="45"/>
@@ -37856,7 +38206,7 @@
         <v>03C2</v>
       </c>
       <c r="C962" t="s">
-        <v>2278</v>
+        <v>2277</v>
       </c>
       <c r="D962" t="str">
         <f t="shared" si="45"/>
@@ -37873,7 +38223,7 @@
         <v>03C3</v>
       </c>
       <c r="C963" t="s">
-        <v>2279</v>
+        <v>2278</v>
       </c>
       <c r="D963" t="str">
         <f t="shared" si="45"/>
@@ -37890,7 +38240,7 @@
         <v>03C4</v>
       </c>
       <c r="C964" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="D964" t="str">
         <f t="shared" si="45"/>
@@ -37907,7 +38257,7 @@
         <v>03C5</v>
       </c>
       <c r="C965" t="s">
-        <v>2281</v>
+        <v>2280</v>
       </c>
       <c r="D965" t="str">
         <f t="shared" si="45"/>
@@ -37924,7 +38274,7 @@
         <v>03C6</v>
       </c>
       <c r="C966" t="s">
-        <v>2282</v>
+        <v>2281</v>
       </c>
       <c r="D966" t="str">
         <f t="shared" si="45"/>
@@ -37941,7 +38291,7 @@
         <v>03C7</v>
       </c>
       <c r="C967" t="s">
-        <v>2296</v>
+        <v>2295</v>
       </c>
       <c r="D967" t="str">
         <f t="shared" si="45"/>
